--- a/RELACAO DE MALOTE RECEBIDO SEGURADORA.xlsx
+++ b/RELACAO DE MALOTE RECEBIDO SEGURADORA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EC2CB0-B143-4867-AB7E-0D94D6B1CB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D443617F-B724-48A9-9724-2C9ED8248094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5A1C727-9BF2-4FA6-AD32-FEB667895D86}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="96">
   <si>
     <t>TIPO</t>
   </si>
@@ -327,15 +327,6 @@
   </si>
   <si>
     <t>TATIANNA FERRARO R DOS SANTOS</t>
-  </si>
-  <si>
-    <t>LACOSTE ROYAL</t>
-  </si>
-  <si>
-    <t>999.999.999-99</t>
-  </si>
-  <si>
-    <t>LUMA DE OLIVEIRA</t>
   </si>
 </sst>
 </file>
@@ -917,7 +908,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13FA77C8-C24F-471E-AB32-3FEAD74EC923}">
-  <dimension ref="A1:Y35"/>
+  <dimension ref="A1:Y34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="7"/>
@@ -3452,79 +3443,6 @@
         <v>46259</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
-        <v>66666</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="I35" s="32">
-        <v>46266</v>
-      </c>
-      <c r="J35" s="6">
-        <v>59.38</v>
-      </c>
-      <c r="K35" s="5">
-        <v>453250.35</v>
-      </c>
-      <c r="L35" s="6">
-        <v>59.38</v>
-      </c>
-      <c r="M35" s="5">
-        <v>453250.35</v>
-      </c>
-      <c r="N35" s="5">
-        <v>45.7</v>
-      </c>
-      <c r="O35" s="5">
-        <v>453250.35</v>
-      </c>
-      <c r="P35" s="5">
-        <v>45.7</v>
-      </c>
-      <c r="Q35" s="5">
-        <v>453250.35</v>
-      </c>
-      <c r="R35" s="5">
-        <v>0</v>
-      </c>
-      <c r="S35" s="5">
-        <v>0</v>
-      </c>
-      <c r="T35" s="5">
-        <v>0</v>
-      </c>
-      <c r="U35" s="17">
-        <v>0</v>
-      </c>
-      <c r="V35" s="14">
-        <f t="shared" ref="V35" si="6">SUM(T35,R35,P35,N35,L35,J35)</f>
-        <v>210.16</v>
-      </c>
-      <c r="W35" s="15"/>
-      <c r="X35" s="16">
-        <v>46259</v>
-      </c>
-    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A16:X22">
     <sortCondition ref="F16:F22"/>

--- a/RELACAO DE MALOTE RECEBIDO SEGURADORA.xlsx
+++ b/RELACAO DE MALOTE RECEBIDO SEGURADORA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D443617F-B724-48A9-9724-2C9ED8248094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974212F6-4BB1-41F0-805B-C16E683E27E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5A1C727-9BF2-4FA6-AD32-FEB667895D86}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="120">
   <si>
     <t>TIPO</t>
   </si>
@@ -327,6 +327,78 @@
   </si>
   <si>
     <t>TATIANNA FERRARO R DOS SANTOS</t>
+  </si>
+  <si>
+    <t>essa participante possui adicional de 1%</t>
+  </si>
+  <si>
+    <t>Implantada</t>
+  </si>
+  <si>
+    <t>E4E - FUMPRESC - FLORIPAPREV PDF</t>
+  </si>
+  <si>
+    <t>GLAUCIO PEREIRA DE SOUZA</t>
+  </si>
+  <si>
+    <t>DOUGLAS MANOEL GUIMARAES</t>
+  </si>
+  <si>
+    <t>MIRIANE PEREIRA DREWS</t>
+  </si>
+  <si>
+    <t>MAURICIO JOSE SANTOS MOREIRA</t>
+  </si>
+  <si>
+    <t>852.034.167-53</t>
+  </si>
+  <si>
+    <t>088.158.889-00</t>
+  </si>
+  <si>
+    <t>076.606.299-64</t>
+  </si>
+  <si>
+    <t>006.837.970-69</t>
+  </si>
+  <si>
+    <t>ADESAO AUTOMATICA</t>
+  </si>
+  <si>
+    <t>ANDRESSA PEDRO BARBOSA</t>
+  </si>
+  <si>
+    <t>022.110.480-13</t>
+  </si>
+  <si>
+    <t>CITRYA JAKELLINNE ALVES SOUSA</t>
+  </si>
+  <si>
+    <t>003.346.871-01</t>
+  </si>
+  <si>
+    <t>DAMARIS BORGES CONSENTINS ANTUNES</t>
+  </si>
+  <si>
+    <t>013.040.130-73</t>
+  </si>
+  <si>
+    <t>DORA CAROLINA DIEDRICH SALDANHA</t>
+  </si>
+  <si>
+    <t>095.356.429-01</t>
+  </si>
+  <si>
+    <t>PAULO RICARDO ILHA JIQUIRICA</t>
+  </si>
+  <si>
+    <t>140.607.718-64</t>
+  </si>
+  <si>
+    <t>SAMAN BELIZARIO BROERING</t>
+  </si>
+  <si>
+    <t>055.912.859-29</t>
   </si>
 </sst>
 </file>
@@ -411,7 +483,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -454,6 +526,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -482,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -524,6 +602,9 @@
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -543,6 +624,9 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="4" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -558,6 +642,9 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="4" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -565,14 +652,50 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -580,6 +703,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFF99"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -908,30 +1036,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13FA77C8-C24F-471E-AB32-3FEAD74EC923}">
-  <dimension ref="A1:Y34"/>
+  <dimension ref="A1:Y44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="7"/>
-    <col min="2" max="2" width="14.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="20.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="53.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="38" style="35" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="53" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="21.75" style="1" customWidth="1"/>
-    <col min="14" max="14" width="21.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="21.75" style="1" customWidth="1"/>
-    <col min="18" max="18" width="29.5" style="1" customWidth="1"/>
-    <col min="19" max="19" width="22.125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="29" style="1" customWidth="1"/>
-    <col min="21" max="21" width="21.75" style="1" customWidth="1"/>
-    <col min="22" max="22" width="14" style="1" customWidth="1"/>
-    <col min="23" max="23" width="20.5" style="1" customWidth="1"/>
-    <col min="24" max="24" width="28.75" style="1" customWidth="1"/>
-    <col min="25" max="16384" width="9" style="1"/>
+    <col min="10" max="10" width="28.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="33.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="33.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="28.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="28.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="15.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="47.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1009,74 +1140,74 @@
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="18">
+      <c r="A2" s="19">
         <v>53946</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="21">
         <v>115935528</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="20" t="s">
+      <c r="D2" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="30">
+      <c r="I2" s="23">
         <v>46235</v>
       </c>
-      <c r="J2" s="22">
+      <c r="J2" s="24">
         <v>6.62</v>
       </c>
-      <c r="K2" s="22">
+      <c r="K2" s="24">
         <v>20319.400000000001</v>
       </c>
-      <c r="L2" s="22">
+      <c r="L2" s="24">
         <v>6.62</v>
       </c>
-      <c r="M2" s="22">
+      <c r="M2" s="24">
         <v>20319.400000000001</v>
       </c>
-      <c r="N2" s="22">
+      <c r="N2" s="24">
         <v>3.43</v>
       </c>
-      <c r="O2" s="22">
+      <c r="O2" s="24">
         <v>20319.400000000001</v>
       </c>
-      <c r="P2" s="22">
+      <c r="P2" s="24">
         <v>3.43</v>
       </c>
-      <c r="Q2" s="22">
+      <c r="Q2" s="24">
         <v>20319.400000000001</v>
       </c>
-      <c r="R2" s="22">
-        <v>0</v>
-      </c>
-      <c r="S2" s="22">
-        <v>0</v>
-      </c>
-      <c r="T2" s="22">
+      <c r="R2" s="24">
+        <v>0</v>
+      </c>
+      <c r="S2" s="24">
+        <v>0</v>
+      </c>
+      <c r="T2" s="24">
         <v>50</v>
       </c>
-      <c r="U2" s="22">
+      <c r="U2" s="24">
         <v>295857.99</v>
       </c>
-      <c r="V2" s="23">
+      <c r="V2" s="25">
         <f>SUM(J2,L2,N2,P2,R2,T2)</f>
         <v>70.099999999999994</v>
       </c>
-      <c r="W2" s="22" t="s">
+      <c r="W2" s="24" t="s">
         <v>9</v>
       </c>
       <c r="X2" s="3">
@@ -1087,74 +1218,74 @@
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="18">
+      <c r="A3" s="19">
         <v>62590</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="21">
         <v>115937631</v>
       </c>
-      <c r="D3" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="30">
+      <c r="I3" s="23">
         <v>46235</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="24">
         <v>140.44</v>
       </c>
-      <c r="K3" s="22">
+      <c r="K3" s="24">
         <v>431385.89</v>
       </c>
-      <c r="L3" s="22">
+      <c r="L3" s="24">
         <v>140.44</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="24">
         <v>431385.89</v>
       </c>
-      <c r="N3" s="22">
+      <c r="N3" s="24">
         <v>72.900000000000006</v>
       </c>
-      <c r="O3" s="22">
+      <c r="O3" s="24">
         <v>431385.89</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="24">
         <v>72.900000000000006</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="24">
         <v>431385.89</v>
       </c>
-      <c r="R3" s="22">
+      <c r="R3" s="24">
         <v>200</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="24">
         <v>614326.07999999996</v>
       </c>
-      <c r="T3" s="22">
+      <c r="T3" s="24">
         <v>100</v>
       </c>
-      <c r="U3" s="22">
+      <c r="U3" s="24">
         <v>591715.98</v>
       </c>
-      <c r="V3" s="23">
+      <c r="V3" s="25">
         <f t="shared" ref="V3:V5" si="0">SUM(J3,L3,N3,P3,R3,T3)</f>
         <v>726.68</v>
       </c>
-      <c r="W3" s="22" t="s">
+      <c r="W3" s="24" t="s">
         <v>9</v>
       </c>
       <c r="X3" s="3">
@@ -1162,74 +1293,74 @@
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="18">
+      <c r="A4" s="19">
         <v>55064</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="21">
         <v>115937636</v>
       </c>
-      <c r="D4" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="20" t="s">
+      <c r="D4" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="23">
         <v>46235</v>
       </c>
-      <c r="J4" s="22">
+      <c r="J4" s="24">
         <v>52.87</v>
       </c>
-      <c r="K4" s="22">
+      <c r="K4" s="24">
         <v>274950.17</v>
       </c>
-      <c r="L4" s="22">
+      <c r="L4" s="24">
         <v>52.87</v>
       </c>
-      <c r="M4" s="22">
+      <c r="M4" s="24">
         <v>274950.17</v>
       </c>
-      <c r="N4" s="22">
+      <c r="N4" s="24">
         <v>35.01</v>
       </c>
-      <c r="O4" s="22">
+      <c r="O4" s="24">
         <v>274950.17</v>
       </c>
-      <c r="P4" s="22">
+      <c r="P4" s="24">
         <v>35.01</v>
       </c>
-      <c r="Q4" s="22">
+      <c r="Q4" s="24">
         <v>274950.17</v>
       </c>
-      <c r="R4" s="22">
-        <v>0</v>
-      </c>
-      <c r="S4" s="22">
-        <v>0</v>
-      </c>
-      <c r="T4" s="22">
+      <c r="R4" s="24">
+        <v>0</v>
+      </c>
+      <c r="S4" s="24">
+        <v>0</v>
+      </c>
+      <c r="T4" s="24">
         <v>400</v>
       </c>
-      <c r="U4" s="22">
+      <c r="U4" s="24">
         <v>3141369.48</v>
       </c>
-      <c r="V4" s="23">
+      <c r="V4" s="25">
         <f t="shared" si="0"/>
         <v>575.76</v>
       </c>
-      <c r="W4" s="25" t="s">
+      <c r="W4" s="27" t="s">
         <v>9</v>
       </c>
       <c r="X4" s="3">
@@ -1237,74 +1368,74 @@
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A5" s="18">
+      <c r="A5" s="19">
         <v>55054</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="21">
         <v>115937635</v>
       </c>
-      <c r="D5" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="20" t="s">
+      <c r="D5" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="23">
         <v>46235</v>
       </c>
-      <c r="J5" s="22">
+      <c r="J5" s="24">
         <v>50.22</v>
       </c>
-      <c r="K5" s="22">
+      <c r="K5" s="24">
         <v>261159.56</v>
       </c>
-      <c r="L5" s="22">
+      <c r="L5" s="24">
         <v>50.22</v>
       </c>
-      <c r="M5" s="22">
+      <c r="M5" s="24">
         <v>261159.56</v>
       </c>
-      <c r="N5" s="22">
+      <c r="N5" s="24">
         <v>33.25</v>
       </c>
-      <c r="O5" s="22">
+      <c r="O5" s="24">
         <v>261159.56</v>
       </c>
-      <c r="P5" s="22">
+      <c r="P5" s="24">
         <v>33.25</v>
       </c>
-      <c r="Q5" s="22">
+      <c r="Q5" s="24">
         <v>261159.56</v>
       </c>
-      <c r="R5" s="22">
-        <v>0</v>
-      </c>
-      <c r="S5" s="22">
-        <v>0</v>
-      </c>
-      <c r="T5" s="22">
-        <v>0</v>
-      </c>
-      <c r="U5" s="22">
-        <v>0</v>
-      </c>
-      <c r="V5" s="23">
+      <c r="R5" s="24">
+        <v>0</v>
+      </c>
+      <c r="S5" s="24">
+        <v>0</v>
+      </c>
+      <c r="T5" s="24">
+        <v>0</v>
+      </c>
+      <c r="U5" s="24">
+        <v>0</v>
+      </c>
+      <c r="V5" s="25">
         <f t="shared" si="0"/>
         <v>166.94</v>
       </c>
-      <c r="W5" s="25" t="s">
+      <c r="W5" s="27" t="s">
         <v>9</v>
       </c>
       <c r="X5" s="3">
@@ -1312,74 +1443,74 @@
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="18">
+      <c r="A6" s="19">
         <v>62592</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="19">
         <v>115937633</v>
       </c>
-      <c r="D6" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="18" t="s">
+      <c r="D6" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="26" t="s">
+      <c r="H6" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="31">
+      <c r="I6" s="29">
         <v>46235</v>
       </c>
-      <c r="J6" s="27">
+      <c r="J6" s="30">
         <v>181.54</v>
       </c>
-      <c r="K6" s="27">
+      <c r="K6" s="30">
         <v>557631.23</v>
       </c>
-      <c r="L6" s="27">
+      <c r="L6" s="30">
         <v>181.54</v>
       </c>
-      <c r="M6" s="27">
+      <c r="M6" s="30">
         <v>557631.23</v>
       </c>
-      <c r="N6" s="27">
+      <c r="N6" s="30">
         <v>94.24</v>
       </c>
-      <c r="O6" s="27">
+      <c r="O6" s="30">
         <v>557631.23</v>
       </c>
-      <c r="P6" s="27">
+      <c r="P6" s="30">
         <v>94.24</v>
       </c>
-      <c r="Q6" s="27">
+      <c r="Q6" s="30">
         <v>557631.23</v>
       </c>
-      <c r="R6" s="27">
-        <v>0</v>
-      </c>
-      <c r="S6" s="27">
-        <v>0</v>
-      </c>
-      <c r="T6" s="27">
+      <c r="R6" s="30">
+        <v>0</v>
+      </c>
+      <c r="S6" s="30">
+        <v>0</v>
+      </c>
+      <c r="T6" s="30">
         <v>300</v>
       </c>
-      <c r="U6" s="27">
+      <c r="U6" s="30">
         <v>1775147.93</v>
       </c>
-      <c r="V6" s="28">
+      <c r="V6" s="31">
         <f>SUM(T6,R6,P6,N6,L6,J6)</f>
         <v>851.56</v>
       </c>
-      <c r="W6" s="27" t="s">
+      <c r="W6" s="30" t="s">
         <v>9</v>
       </c>
       <c r="X6" s="3">
@@ -1387,74 +1518,74 @@
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A7" s="18">
+      <c r="A7" s="19">
         <v>62596</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="19">
         <v>115937634</v>
       </c>
-      <c r="D7" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="18" t="s">
+      <c r="D7" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="H7" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="29">
         <v>46235</v>
       </c>
-      <c r="J7" s="27">
+      <c r="J7" s="30">
         <v>241.41</v>
       </c>
-      <c r="K7" s="27">
+      <c r="K7" s="30">
         <v>741534.7</v>
       </c>
-      <c r="L7" s="27">
+      <c r="L7" s="30">
         <v>241.41</v>
       </c>
-      <c r="M7" s="27">
+      <c r="M7" s="30">
         <v>741534.7</v>
       </c>
-      <c r="N7" s="27">
+      <c r="N7" s="30">
         <v>125.32</v>
       </c>
-      <c r="O7" s="27">
+      <c r="O7" s="30">
         <v>741534.7</v>
       </c>
-      <c r="P7" s="27">
+      <c r="P7" s="30">
         <v>125.32</v>
       </c>
-      <c r="Q7" s="27">
+      <c r="Q7" s="30">
         <v>741534.7</v>
       </c>
-      <c r="R7" s="27">
+      <c r="R7" s="30">
         <v>100</v>
       </c>
-      <c r="S7" s="27">
+      <c r="S7" s="30">
         <v>307163.03999999998</v>
       </c>
-      <c r="T7" s="27">
+      <c r="T7" s="30">
         <v>150</v>
       </c>
-      <c r="U7" s="27">
+      <c r="U7" s="30">
         <v>887573.96</v>
       </c>
-      <c r="V7" s="28">
+      <c r="V7" s="31">
         <f t="shared" ref="V7:V15" si="1">SUM(T7,R7,P7,N7,L7,J7)</f>
         <v>983.45999999999992</v>
       </c>
-      <c r="W7" s="27" t="s">
+      <c r="W7" s="30" t="s">
         <v>9</v>
       </c>
       <c r="X7" s="3">
@@ -1462,74 +1593,74 @@
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="18">
+      <c r="A8" s="19">
         <v>56516</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="19">
         <v>115937638</v>
       </c>
-      <c r="D8" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="18" t="s">
+      <c r="D8" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="26" t="s">
+      <c r="H8" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="29">
         <v>46235</v>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="30">
         <v>42.23</v>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="30">
         <v>322355.37</v>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="30">
         <v>42.23</v>
       </c>
-      <c r="M8" s="27">
+      <c r="M8" s="30">
         <v>322355.37</v>
       </c>
-      <c r="N8" s="27">
+      <c r="N8" s="30">
         <v>32.5</v>
       </c>
-      <c r="O8" s="27">
+      <c r="O8" s="30">
         <v>322355.37</v>
       </c>
-      <c r="P8" s="27">
+      <c r="P8" s="30">
         <v>32.5</v>
       </c>
-      <c r="Q8" s="27">
+      <c r="Q8" s="30">
         <v>322355.37</v>
       </c>
-      <c r="R8" s="27">
-        <v>0</v>
-      </c>
-      <c r="S8" s="27">
-        <v>0</v>
-      </c>
-      <c r="T8" s="27">
-        <v>0</v>
-      </c>
-      <c r="U8" s="27">
-        <v>0</v>
-      </c>
-      <c r="V8" s="28">
+      <c r="R8" s="30">
+        <v>0</v>
+      </c>
+      <c r="S8" s="30">
+        <v>0</v>
+      </c>
+      <c r="T8" s="30">
+        <v>0</v>
+      </c>
+      <c r="U8" s="30">
+        <v>0</v>
+      </c>
+      <c r="V8" s="31">
         <f t="shared" si="1"/>
         <v>149.45999999999998</v>
       </c>
-      <c r="W8" s="18" t="s">
+      <c r="W8" s="19" t="s">
         <v>9</v>
       </c>
       <c r="X8" s="3">
@@ -1537,74 +1668,74 @@
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A9" s="18">
+      <c r="A9" s="19">
         <v>62594</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <v>115937639</v>
       </c>
-      <c r="D9" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="18" t="s">
+      <c r="D9" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="H9" s="26" t="s">
+      <c r="H9" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="29">
         <v>46235</v>
       </c>
-      <c r="J9" s="27">
+      <c r="J9" s="30">
         <v>58.54</v>
       </c>
-      <c r="K9" s="27">
+      <c r="K9" s="30">
         <v>304424.75</v>
       </c>
-      <c r="L9" s="27">
+      <c r="L9" s="30">
         <v>58.54</v>
       </c>
-      <c r="M9" s="27">
+      <c r="M9" s="30">
         <v>304424.75</v>
       </c>
-      <c r="N9" s="27">
+      <c r="N9" s="30">
         <v>38.76</v>
       </c>
-      <c r="O9" s="27">
+      <c r="O9" s="30">
         <v>304424.75</v>
       </c>
-      <c r="P9" s="27">
+      <c r="P9" s="30">
         <v>38.76</v>
       </c>
-      <c r="Q9" s="27">
+      <c r="Q9" s="30">
         <v>304424.75</v>
       </c>
-      <c r="R9" s="27">
+      <c r="R9" s="30">
         <v>175</v>
       </c>
-      <c r="S9" s="27">
+      <c r="S9" s="30">
         <v>910045.87</v>
       </c>
-      <c r="T9" s="27">
+      <c r="T9" s="30">
         <v>125</v>
       </c>
-      <c r="U9" s="27">
+      <c r="U9" s="30">
         <v>981677.96</v>
       </c>
-      <c r="V9" s="28">
+      <c r="V9" s="31">
         <f t="shared" si="1"/>
         <v>494.6</v>
       </c>
-      <c r="W9" s="18" t="s">
+      <c r="W9" s="19" t="s">
         <v>9</v>
       </c>
       <c r="X9" s="3">
@@ -1612,74 +1743,74 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A10" s="18">
+      <c r="A10" s="19">
         <v>54015</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="19">
         <v>115971164</v>
       </c>
-      <c r="D10" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="18" t="s">
+      <c r="D10" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="G10" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="26" t="s">
+      <c r="H10" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="I10" s="31">
+      <c r="I10" s="29">
         <v>46235</v>
       </c>
-      <c r="J10" s="27">
+      <c r="J10" s="30">
         <v>37.090000000000003</v>
       </c>
-      <c r="K10" s="27">
+      <c r="K10" s="30">
         <v>113915.44</v>
       </c>
-      <c r="L10" s="27">
+      <c r="L10" s="30">
         <v>37.090000000000003</v>
       </c>
-      <c r="M10" s="27">
+      <c r="M10" s="30">
         <v>113915.44</v>
       </c>
-      <c r="N10" s="27">
+      <c r="N10" s="30">
         <v>19.25</v>
       </c>
-      <c r="O10" s="27">
+      <c r="O10" s="30">
         <v>113915.44</v>
       </c>
-      <c r="P10" s="27">
+      <c r="P10" s="30">
         <v>19.25</v>
       </c>
-      <c r="Q10" s="27">
+      <c r="Q10" s="30">
         <v>113915.44</v>
       </c>
-      <c r="R10" s="27">
-        <v>0</v>
-      </c>
-      <c r="S10" s="27">
-        <v>0</v>
-      </c>
-      <c r="T10" s="27">
-        <v>0</v>
-      </c>
-      <c r="U10" s="27">
-        <v>0</v>
-      </c>
-      <c r="V10" s="28">
+      <c r="R10" s="30">
+        <v>0</v>
+      </c>
+      <c r="S10" s="30">
+        <v>0</v>
+      </c>
+      <c r="T10" s="30">
+        <v>0</v>
+      </c>
+      <c r="U10" s="30">
+        <v>0</v>
+      </c>
+      <c r="V10" s="31">
         <f t="shared" si="1"/>
         <v>112.68</v>
       </c>
-      <c r="W10" s="27" t="s">
+      <c r="W10" s="30" t="s">
         <v>9</v>
       </c>
       <c r="X10" s="3">
@@ -1687,74 +1818,74 @@
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A11" s="18">
+      <c r="A11" s="19">
         <v>54059</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="19">
         <v>115971165</v>
       </c>
-      <c r="D11" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="18" t="s">
+      <c r="D11" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="26" t="s">
+      <c r="G11" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="H11" s="26" t="s">
+      <c r="H11" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="29">
         <v>46235</v>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="30">
         <v>26.45</v>
       </c>
-      <c r="K11" s="27">
+      <c r="K11" s="30">
         <v>137571.42000000001</v>
       </c>
-      <c r="L11" s="27">
+      <c r="L11" s="30">
         <v>26.45</v>
       </c>
-      <c r="M11" s="27">
+      <c r="M11" s="30">
         <v>137571.42000000001</v>
       </c>
-      <c r="N11" s="27">
+      <c r="N11" s="30">
         <v>17.52</v>
       </c>
-      <c r="O11" s="27">
+      <c r="O11" s="30">
         <v>137571.42000000001</v>
       </c>
-      <c r="P11" s="27">
+      <c r="P11" s="30">
         <v>17.52</v>
       </c>
-      <c r="Q11" s="27">
+      <c r="Q11" s="30">
         <v>137571.42000000001</v>
       </c>
-      <c r="R11" s="27">
+      <c r="R11" s="30">
         <v>35</v>
       </c>
-      <c r="S11" s="27">
+      <c r="S11" s="30">
         <v>182009.17</v>
       </c>
-      <c r="T11" s="27">
+      <c r="T11" s="30">
         <v>35</v>
       </c>
-      <c r="U11" s="27">
+      <c r="U11" s="30">
         <v>274869.83</v>
       </c>
-      <c r="V11" s="28">
+      <c r="V11" s="31">
         <f t="shared" si="1"/>
         <v>157.93999999999997</v>
       </c>
-      <c r="W11" s="27" t="s">
+      <c r="W11" s="30" t="s">
         <v>9</v>
       </c>
       <c r="X11" s="3">
@@ -1762,74 +1893,74 @@
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="18">
+      <c r="A12" s="19">
         <v>54055</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="19">
         <v>115971166</v>
       </c>
-      <c r="D12" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="18" t="s">
+      <c r="D12" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="26" t="s">
+      <c r="G12" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="H12" s="26" t="s">
+      <c r="H12" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="I12" s="31">
+      <c r="I12" s="29">
         <v>46235</v>
       </c>
-      <c r="J12" s="27">
+      <c r="J12" s="30">
         <v>34.04</v>
       </c>
-      <c r="K12" s="27">
+      <c r="K12" s="30">
         <v>177018.17</v>
       </c>
-      <c r="L12" s="27">
+      <c r="L12" s="30">
         <v>34.04</v>
       </c>
-      <c r="M12" s="27">
+      <c r="M12" s="30">
         <v>177018.17</v>
       </c>
-      <c r="N12" s="27">
+      <c r="N12" s="30">
         <v>22.54</v>
       </c>
-      <c r="O12" s="27">
+      <c r="O12" s="30">
         <v>177018.17</v>
       </c>
-      <c r="P12" s="27">
+      <c r="P12" s="30">
         <v>22.54</v>
       </c>
-      <c r="Q12" s="27">
+      <c r="Q12" s="30">
         <v>177018.17</v>
       </c>
-      <c r="R12" s="27">
+      <c r="R12" s="30">
         <v>50</v>
       </c>
-      <c r="S12" s="27">
+      <c r="S12" s="30">
         <v>260013.1</v>
       </c>
-      <c r="T12" s="27">
+      <c r="T12" s="30">
         <v>50</v>
       </c>
-      <c r="U12" s="27">
+      <c r="U12" s="30">
         <v>392671.19</v>
       </c>
-      <c r="V12" s="28">
+      <c r="V12" s="31">
         <f t="shared" si="1"/>
         <v>213.15999999999997</v>
       </c>
-      <c r="W12" s="18" t="s">
+      <c r="W12" s="19" t="s">
         <v>9</v>
       </c>
       <c r="X12" s="3">
@@ -1837,74 +1968,74 @@
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="18">
+      <c r="A13" s="19">
         <v>64986</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="19">
         <v>115937643</v>
       </c>
-      <c r="D13" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="18" t="s">
+      <c r="D13" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="26" t="s">
+      <c r="F13" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="G13" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="26" t="s">
+      <c r="H13" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="I13" s="31">
+      <c r="I13" s="29">
         <v>46235</v>
       </c>
-      <c r="J13" s="27">
+      <c r="J13" s="30">
         <v>157.27000000000001</v>
       </c>
-      <c r="K13" s="27">
+      <c r="K13" s="30">
         <v>817869.15</v>
       </c>
-      <c r="L13" s="27">
+      <c r="L13" s="30">
         <v>157.27000000000001</v>
       </c>
-      <c r="M13" s="27">
+      <c r="M13" s="30">
         <v>817869.15</v>
       </c>
-      <c r="N13" s="27">
+      <c r="N13" s="30">
         <v>104.14</v>
       </c>
-      <c r="O13" s="27">
+      <c r="O13" s="30">
         <v>817869.15</v>
       </c>
-      <c r="P13" s="27">
+      <c r="P13" s="30">
         <v>104.14</v>
       </c>
-      <c r="Q13" s="27">
+      <c r="Q13" s="30">
         <v>817869.15</v>
       </c>
-      <c r="R13" s="27">
+      <c r="R13" s="30">
         <v>600</v>
       </c>
-      <c r="S13" s="27">
+      <c r="S13" s="30">
         <v>3120157.26</v>
       </c>
-      <c r="T13" s="27">
+      <c r="T13" s="30">
         <v>550</v>
       </c>
-      <c r="U13" s="27">
+      <c r="U13" s="30">
         <v>4319383.04</v>
       </c>
-      <c r="V13" s="28">
+      <c r="V13" s="31">
         <f t="shared" si="1"/>
         <v>1672.8200000000002</v>
       </c>
-      <c r="W13" s="18" t="s">
+      <c r="W13" s="19" t="s">
         <v>9</v>
       </c>
       <c r="X13" s="3">
@@ -1924,7 +2055,7 @@
       <c r="D14" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F14" s="9" t="s">
@@ -1936,7 +2067,7 @@
       <c r="H14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="15">
         <v>46266</v>
       </c>
       <c r="J14" s="5">
@@ -1999,7 +2130,7 @@
       <c r="D15" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F15" s="9" t="s">
@@ -2011,7 +2142,7 @@
       <c r="H15" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="32">
+      <c r="I15" s="15">
         <v>46266</v>
       </c>
       <c r="J15" s="5">
@@ -2074,7 +2205,7 @@
       <c r="D16" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F16" s="9" t="s">
@@ -2084,7 +2215,7 @@
         <v>59</v>
       </c>
       <c r="H16" s="9"/>
-      <c r="I16" s="32">
+      <c r="I16" s="15">
         <v>46266</v>
       </c>
       <c r="J16" s="6">
@@ -2127,8 +2258,8 @@
         <f t="shared" ref="V16:V22" si="2">SUM(T16,R16,P16,N16,L16,J16)</f>
         <v>439.4</v>
       </c>
-      <c r="W16" s="15"/>
-      <c r="X16" s="16">
+      <c r="W16" s="16"/>
+      <c r="X16" s="17">
         <v>46241</v>
       </c>
     </row>
@@ -2145,7 +2276,7 @@
       <c r="D17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F17" s="9" t="s">
@@ -2157,7 +2288,7 @@
       <c r="H17" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I17" s="32">
+      <c r="I17" s="15">
         <v>46266</v>
       </c>
       <c r="J17" s="6">
@@ -2184,24 +2315,24 @@
       <c r="Q17" s="5">
         <v>317460.47999999998</v>
       </c>
-      <c r="R17" s="17">
-        <v>0</v>
-      </c>
-      <c r="S17" s="17">
-        <v>0</v>
-      </c>
-      <c r="T17" s="17">
-        <v>0</v>
-      </c>
-      <c r="U17" s="17">
+      <c r="R17" s="18">
+        <v>0</v>
+      </c>
+      <c r="S17" s="18">
+        <v>0</v>
+      </c>
+      <c r="T17" s="18">
+        <v>0</v>
+      </c>
+      <c r="U17" s="18">
         <v>0</v>
       </c>
       <c r="V17" s="14">
         <f t="shared" si="2"/>
         <v>147.19999999999999</v>
       </c>
-      <c r="W17" s="15"/>
-      <c r="X17" s="16">
+      <c r="W17" s="16"/>
+      <c r="X17" s="17">
         <v>46241</v>
       </c>
     </row>
@@ -2218,7 +2349,7 @@
       <c r="D18" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F18" s="9" t="s">
@@ -2228,7 +2359,7 @@
         <v>57</v>
       </c>
       <c r="H18" s="9"/>
-      <c r="I18" s="32">
+      <c r="I18" s="15">
         <v>46266</v>
       </c>
       <c r="J18" s="6">
@@ -2271,8 +2402,8 @@
         <f t="shared" si="2"/>
         <v>49.96</v>
       </c>
-      <c r="W18" s="15"/>
-      <c r="X18" s="16">
+      <c r="W18" s="16"/>
+      <c r="X18" s="17">
         <v>46241</v>
       </c>
     </row>
@@ -2289,7 +2420,7 @@
       <c r="D19" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F19" s="9" t="s">
@@ -2301,7 +2432,7 @@
       <c r="H19" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I19" s="32">
+      <c r="I19" s="15">
         <v>46266</v>
       </c>
       <c r="J19" s="6">
@@ -2344,8 +2475,8 @@
         <f t="shared" si="2"/>
         <v>118.27999999999999</v>
       </c>
-      <c r="W19" s="15"/>
-      <c r="X19" s="16">
+      <c r="W19" s="16"/>
+      <c r="X19" s="17">
         <v>46241</v>
       </c>
     </row>
@@ -2362,7 +2493,7 @@
       <c r="D20" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F20" s="9" t="s">
@@ -2374,7 +2505,7 @@
       <c r="H20" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I20" s="32">
+      <c r="I20" s="15">
         <v>46266</v>
       </c>
       <c r="J20" s="6">
@@ -2417,8 +2548,8 @@
         <f t="shared" si="2"/>
         <v>125.4</v>
       </c>
-      <c r="W20" s="15"/>
-      <c r="X20" s="16">
+      <c r="W20" s="16"/>
+      <c r="X20" s="17">
         <v>46241</v>
       </c>
     </row>
@@ -2435,7 +2566,7 @@
       <c r="D21" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F21" s="9" t="s">
@@ -2445,7 +2576,7 @@
         <v>63</v>
       </c>
       <c r="H21" s="9"/>
-      <c r="I21" s="32">
+      <c r="I21" s="15">
         <v>46266</v>
       </c>
       <c r="J21" s="6">
@@ -2488,8 +2619,8 @@
         <f t="shared" si="2"/>
         <v>324.52</v>
       </c>
-      <c r="W21" s="15"/>
-      <c r="X21" s="16">
+      <c r="W21" s="16"/>
+      <c r="X21" s="17">
         <v>46241</v>
       </c>
     </row>
@@ -2506,7 +2637,7 @@
       <c r="D22" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F22" s="9" t="s">
@@ -2518,7 +2649,7 @@
       <c r="H22" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I22" s="32">
+      <c r="I22" s="15">
         <v>46266</v>
       </c>
       <c r="J22" s="6">
@@ -2554,15 +2685,15 @@
       <c r="T22" s="5">
         <v>0</v>
       </c>
-      <c r="U22" s="17">
+      <c r="U22" s="18">
         <v>0</v>
       </c>
       <c r="V22" s="14">
         <f t="shared" si="2"/>
         <v>101.62</v>
       </c>
-      <c r="W22" s="15"/>
-      <c r="X22" s="16">
+      <c r="W22" s="16"/>
+      <c r="X22" s="17">
         <v>46241</v>
       </c>
     </row>
@@ -2579,7 +2710,7 @@
       <c r="D23" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F23" s="9" t="s">
@@ -2591,7 +2722,7 @@
       <c r="H23" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I23" s="32">
+      <c r="I23" s="15">
         <v>46266</v>
       </c>
       <c r="J23" s="6">
@@ -2634,8 +2765,8 @@
         <f t="shared" ref="V23:V25" si="3">SUM(T23,R23,P23,N23,L23,J23)</f>
         <v>18.68</v>
       </c>
-      <c r="W23" s="15"/>
-      <c r="X23" s="16">
+      <c r="W23" s="16"/>
+      <c r="X23" s="17">
         <v>46251</v>
       </c>
     </row>
@@ -2652,7 +2783,7 @@
       <c r="D24" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F24" s="9" t="s">
@@ -2664,7 +2795,7 @@
       <c r="H24" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="15">
         <v>46266</v>
       </c>
       <c r="J24" s="6">
@@ -2707,8 +2838,8 @@
         <f t="shared" si="3"/>
         <v>176.68</v>
       </c>
-      <c r="W24" s="15"/>
-      <c r="X24" s="16">
+      <c r="W24" s="16"/>
+      <c r="X24" s="17">
         <v>46251</v>
       </c>
     </row>
@@ -2725,7 +2856,7 @@
       <c r="D25" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F25" s="9" t="s">
@@ -2737,7 +2868,7 @@
       <c r="H25" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I25" s="32">
+      <c r="I25" s="15">
         <v>46266</v>
       </c>
       <c r="J25" s="6">
@@ -2773,15 +2904,15 @@
       <c r="T25" s="5">
         <v>0</v>
       </c>
-      <c r="U25" s="17">
+      <c r="U25" s="18">
         <v>0</v>
       </c>
       <c r="V25" s="14">
         <f t="shared" si="3"/>
         <v>94.58</v>
       </c>
-      <c r="W25" s="15"/>
-      <c r="X25" s="16">
+      <c r="W25" s="16"/>
+      <c r="X25" s="17">
         <v>46251</v>
       </c>
     </row>
@@ -2798,7 +2929,7 @@
       <c r="D26" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F26" s="9" t="s">
@@ -2810,7 +2941,7 @@
       <c r="H26" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I26" s="32">
+      <c r="I26" s="15">
         <v>46266</v>
       </c>
       <c r="J26" s="6">
@@ -2853,8 +2984,8 @@
         <f t="shared" ref="V26:V28" si="4">SUM(T26,R26,P26,N26,L26,J26)</f>
         <v>115.28</v>
       </c>
-      <c r="W26" s="15"/>
-      <c r="X26" s="16">
+      <c r="W26" s="16"/>
+      <c r="X26" s="17">
         <v>46255</v>
       </c>
     </row>
@@ -2871,7 +3002,7 @@
       <c r="D27" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F27" s="9" t="s">
@@ -2883,7 +3014,7 @@
       <c r="H27" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="15">
         <v>46266</v>
       </c>
       <c r="J27" s="5">
@@ -2926,8 +3057,8 @@
         <f t="shared" si="4"/>
         <v>453.14</v>
       </c>
-      <c r="W27" s="15"/>
-      <c r="X27" s="16">
+      <c r="W27" s="16"/>
+      <c r="X27" s="17">
         <v>46255</v>
       </c>
     </row>
@@ -2944,7 +3075,7 @@
       <c r="D28" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F28" s="9" t="s">
@@ -2956,7 +3087,7 @@
       <c r="H28" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="15">
         <v>46266</v>
       </c>
       <c r="J28" s="6">
@@ -2992,15 +3123,15 @@
       <c r="T28" s="5">
         <v>0</v>
       </c>
-      <c r="U28" s="17">
+      <c r="U28" s="18">
         <v>0</v>
       </c>
       <c r="V28" s="14">
         <f t="shared" si="4"/>
         <v>139.98000000000002</v>
       </c>
-      <c r="W28" s="15"/>
-      <c r="X28" s="16">
+      <c r="W28" s="16"/>
+      <c r="X28" s="17">
         <v>46255</v>
       </c>
     </row>
@@ -3017,7 +3148,7 @@
       <c r="D29" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F29" s="9" t="s">
@@ -3029,7 +3160,7 @@
       <c r="H29" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I29" s="32">
+      <c r="I29" s="15">
         <v>46266</v>
       </c>
       <c r="J29" s="6">
@@ -3072,11 +3203,13 @@
         <f t="shared" ref="V29:V34" si="5">SUM(T29,R29,P29,N29,L29,J29)</f>
         <v>112.78</v>
       </c>
-      <c r="W29" s="15"/>
-      <c r="X29" s="16">
+      <c r="W29" s="16"/>
+      <c r="X29" s="17">
         <v>46259</v>
       </c>
-      <c r="Y29" s="29"/>
+      <c r="Y29" s="32" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
@@ -3091,7 +3224,7 @@
       <c r="D30" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F30" s="9" t="s">
@@ -3103,7 +3236,7 @@
       <c r="H30" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I30" s="32">
+      <c r="I30" s="15">
         <v>46266</v>
       </c>
       <c r="J30" s="6">
@@ -3146,8 +3279,8 @@
         <f t="shared" si="5"/>
         <v>105.88</v>
       </c>
-      <c r="W30" s="15"/>
-      <c r="X30" s="16">
+      <c r="W30" s="16"/>
+      <c r="X30" s="17">
         <v>46259</v>
       </c>
     </row>
@@ -3164,7 +3297,7 @@
       <c r="D31" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F31" s="9" t="s">
@@ -3176,7 +3309,7 @@
       <c r="H31" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I31" s="32">
+      <c r="I31" s="15">
         <v>46266</v>
       </c>
       <c r="J31" s="6">
@@ -3212,15 +3345,15 @@
       <c r="T31" s="5">
         <v>0</v>
       </c>
-      <c r="U31" s="17">
+      <c r="U31" s="18">
         <v>0</v>
       </c>
       <c r="V31" s="14">
         <f t="shared" si="5"/>
         <v>165.51999999999998</v>
       </c>
-      <c r="W31" s="15"/>
-      <c r="X31" s="16">
+      <c r="W31" s="16"/>
+      <c r="X31" s="17">
         <v>46259</v>
       </c>
     </row>
@@ -3237,7 +3370,7 @@
       <c r="D32" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F32" s="9" t="s">
@@ -3249,7 +3382,7 @@
       <c r="H32" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I32" s="32">
+      <c r="I32" s="15">
         <v>46266</v>
       </c>
       <c r="J32" s="5">
@@ -3292,12 +3425,12 @@
         <f t="shared" si="5"/>
         <v>251.64</v>
       </c>
-      <c r="W32" s="15"/>
-      <c r="X32" s="16">
+      <c r="W32" s="16"/>
+      <c r="X32" s="17">
         <v>46259</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>54746</v>
       </c>
@@ -3310,7 +3443,7 @@
       <c r="D33" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F33" s="9" t="s">
@@ -3322,7 +3455,7 @@
       <c r="H33" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I33" s="32">
+      <c r="I33" s="15">
         <v>46266</v>
       </c>
       <c r="J33" s="5">
@@ -3365,12 +3498,12 @@
         <f t="shared" si="5"/>
         <v>240.26</v>
       </c>
-      <c r="W33" s="15"/>
-      <c r="X33" s="16">
+      <c r="W33" s="16"/>
+      <c r="X33" s="17">
         <v>46259</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>54647</v>
       </c>
@@ -3383,7 +3516,7 @@
       <c r="D34" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="34" t="s">
         <v>10</v>
       </c>
       <c r="F34" s="9" t="s">
@@ -3395,7 +3528,7 @@
       <c r="H34" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I34" s="32">
+      <c r="I34" s="15">
         <v>46266</v>
       </c>
       <c r="J34" s="6">
@@ -3431,16 +3564,759 @@
       <c r="T34" s="5">
         <v>0</v>
       </c>
-      <c r="U34" s="17">
+      <c r="U34" s="18">
         <v>0</v>
       </c>
       <c r="V34" s="14">
         <f t="shared" si="5"/>
         <v>210.16</v>
       </c>
-      <c r="W34" s="15"/>
-      <c r="X34" s="16">
+      <c r="W34" s="16"/>
+      <c r="X34" s="17">
         <v>46259</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>54941</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35" s="6">
+        <v>115971170</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E35" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I35" s="15">
+        <v>46296</v>
+      </c>
+      <c r="J35" s="6">
+        <v>30.63</v>
+      </c>
+      <c r="K35" s="5">
+        <v>24341.48</v>
+      </c>
+      <c r="L35" s="6">
+        <v>30.63</v>
+      </c>
+      <c r="M35" s="5">
+        <v>24341.48</v>
+      </c>
+      <c r="N35" s="6">
+        <v>17.649999999999999</v>
+      </c>
+      <c r="O35" s="5">
+        <v>24341.48</v>
+      </c>
+      <c r="P35" s="6">
+        <v>17.649999999999999</v>
+      </c>
+      <c r="Q35" s="5">
+        <v>24341.48</v>
+      </c>
+      <c r="R35" s="5">
+        <v>0</v>
+      </c>
+      <c r="S35" s="5">
+        <v>0</v>
+      </c>
+      <c r="T35" s="5">
+        <v>200</v>
+      </c>
+      <c r="U35" s="5">
+        <v>275862.07</v>
+      </c>
+      <c r="V35" s="14">
+        <f t="shared" ref="V35:V38" si="6">SUM(T35,R35,P35,N35,L35,J35)</f>
+        <v>296.56</v>
+      </c>
+      <c r="W35" s="16"/>
+      <c r="X35" s="17">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>54160</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="6">
+        <v>115937651</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E36" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" s="15">
+        <v>46296</v>
+      </c>
+      <c r="J36" s="5">
+        <v>0.98</v>
+      </c>
+      <c r="K36" s="5">
+        <v>7460.57</v>
+      </c>
+      <c r="L36" s="5">
+        <v>0.98</v>
+      </c>
+      <c r="M36" s="5">
+        <v>7460.57</v>
+      </c>
+      <c r="N36" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="O36" s="5">
+        <v>7460.57</v>
+      </c>
+      <c r="P36" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="Q36" s="5">
+        <v>7460.57</v>
+      </c>
+      <c r="R36" s="5">
+        <v>0</v>
+      </c>
+      <c r="S36" s="5">
+        <v>0</v>
+      </c>
+      <c r="T36" s="5">
+        <v>0</v>
+      </c>
+      <c r="U36" s="5">
+        <v>0</v>
+      </c>
+      <c r="V36" s="14">
+        <f t="shared" si="6"/>
+        <v>3.46</v>
+      </c>
+      <c r="W36" s="16"/>
+      <c r="X36" s="17">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>54576</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="6">
+        <v>115971178</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E37" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I37" s="15">
+        <v>46296</v>
+      </c>
+      <c r="J37" s="5">
+        <v>18.489999999999998</v>
+      </c>
+      <c r="K37" s="5">
+        <v>141157.96</v>
+      </c>
+      <c r="L37" s="5">
+        <v>18.489999999999998</v>
+      </c>
+      <c r="M37" s="5">
+        <v>141157.96</v>
+      </c>
+      <c r="N37" s="5">
+        <v>14.23</v>
+      </c>
+      <c r="O37" s="5">
+        <v>141157.96</v>
+      </c>
+      <c r="P37" s="5">
+        <v>14.23</v>
+      </c>
+      <c r="Q37" s="5">
+        <v>141157.96</v>
+      </c>
+      <c r="R37" s="5">
+        <v>0</v>
+      </c>
+      <c r="S37" s="5">
+        <v>0</v>
+      </c>
+      <c r="T37" s="5">
+        <v>0</v>
+      </c>
+      <c r="U37" s="5">
+        <v>0</v>
+      </c>
+      <c r="V37" s="14">
+        <f t="shared" si="6"/>
+        <v>65.44</v>
+      </c>
+      <c r="W37" s="16"/>
+      <c r="X37" s="17">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>55069</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="6">
+        <v>115937657</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E38" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="H38" s="9"/>
+      <c r="I38" s="15">
+        <v>46296</v>
+      </c>
+      <c r="J38" s="6">
+        <v>80.37</v>
+      </c>
+      <c r="K38" s="5">
+        <v>246853.96</v>
+      </c>
+      <c r="L38" s="6">
+        <v>80.37</v>
+      </c>
+      <c r="M38" s="5">
+        <v>246853.96</v>
+      </c>
+      <c r="N38" s="6">
+        <v>41.72</v>
+      </c>
+      <c r="O38" s="5">
+        <v>246853.96</v>
+      </c>
+      <c r="P38" s="6">
+        <v>41.72</v>
+      </c>
+      <c r="Q38" s="5">
+        <v>246853.96</v>
+      </c>
+      <c r="R38" s="5">
+        <v>0</v>
+      </c>
+      <c r="S38" s="5">
+        <v>0</v>
+      </c>
+      <c r="T38" s="5">
+        <v>0</v>
+      </c>
+      <c r="U38" s="18">
+        <v>0</v>
+      </c>
+      <c r="V38" s="14">
+        <f t="shared" si="6"/>
+        <v>244.18</v>
+      </c>
+      <c r="W38" s="16"/>
+      <c r="X38" s="17">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A39" s="36">
+        <v>65426</v>
+      </c>
+      <c r="B39" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="C39" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="D39" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="F39" s="39" t="s">
+        <v>108</v>
+      </c>
+      <c r="G39" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="H39" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="I39" s="40">
+        <v>46235</v>
+      </c>
+      <c r="J39" s="41">
+        <v>45.89</v>
+      </c>
+      <c r="K39" s="41">
+        <v>350245.18859999994</v>
+      </c>
+      <c r="L39" s="41">
+        <v>45.89</v>
+      </c>
+      <c r="M39" s="41">
+        <v>350245.18859999994</v>
+      </c>
+      <c r="N39" s="41">
+        <v>35.32</v>
+      </c>
+      <c r="O39" s="41">
+        <v>350245.18859999994</v>
+      </c>
+      <c r="P39" s="41">
+        <v>35.32</v>
+      </c>
+      <c r="Q39" s="41">
+        <v>350245.18859999994</v>
+      </c>
+      <c r="R39" s="41">
+        <v>0</v>
+      </c>
+      <c r="S39" s="41">
+        <v>0</v>
+      </c>
+      <c r="T39" s="41">
+        <v>0</v>
+      </c>
+      <c r="U39" s="41">
+        <v>0</v>
+      </c>
+      <c r="V39" s="42">
+        <f>SUM(J39,L39,N39,P39,R39,T39)</f>
+        <v>162.41999999999999</v>
+      </c>
+      <c r="W39" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="X39" s="3">
+        <v>46267</v>
+      </c>
+      <c r="Y39" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A40" s="36">
+        <v>65427</v>
+      </c>
+      <c r="B40" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="F40" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="G40" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="H40" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="I40" s="40">
+        <v>46235</v>
+      </c>
+      <c r="J40" s="41">
+        <v>55.38</v>
+      </c>
+      <c r="K40" s="41">
+        <v>422667.83069999993</v>
+      </c>
+      <c r="L40" s="41">
+        <v>55.38</v>
+      </c>
+      <c r="M40" s="41">
+        <v>422667.83069999993</v>
+      </c>
+      <c r="N40" s="41">
+        <v>42.62</v>
+      </c>
+      <c r="O40" s="41">
+        <v>422667.83069999993</v>
+      </c>
+      <c r="P40" s="41">
+        <v>42.62</v>
+      </c>
+      <c r="Q40" s="41">
+        <v>422667.83069999993</v>
+      </c>
+      <c r="R40" s="41">
+        <v>0</v>
+      </c>
+      <c r="S40" s="41">
+        <v>0</v>
+      </c>
+      <c r="T40" s="41">
+        <v>0</v>
+      </c>
+      <c r="U40" s="41">
+        <v>0</v>
+      </c>
+      <c r="V40" s="42">
+        <f t="shared" ref="V40:V42" si="7">SUM(J40,L40,N40,P40,R40,T40)</f>
+        <v>196</v>
+      </c>
+      <c r="W40" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="X40" s="3">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A41" s="36">
+        <v>65428</v>
+      </c>
+      <c r="B41" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="C41" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="D41" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="F41" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="G41" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="H41" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="I41" s="40">
+        <v>46235</v>
+      </c>
+      <c r="J41" s="41">
+        <v>18.79</v>
+      </c>
+      <c r="K41" s="41">
+        <v>57712.712499999972</v>
+      </c>
+      <c r="L41" s="41">
+        <v>18.79</v>
+      </c>
+      <c r="M41" s="41">
+        <v>57712.712499999972</v>
+      </c>
+      <c r="N41" s="41">
+        <v>9.75</v>
+      </c>
+      <c r="O41" s="41">
+        <v>57712.712499999972</v>
+      </c>
+      <c r="P41" s="41">
+        <v>9.75</v>
+      </c>
+      <c r="Q41" s="41">
+        <v>57712.712499999972</v>
+      </c>
+      <c r="R41" s="41">
+        <v>0</v>
+      </c>
+      <c r="S41" s="41">
+        <v>0</v>
+      </c>
+      <c r="T41" s="41">
+        <v>0</v>
+      </c>
+      <c r="U41" s="41">
+        <v>0</v>
+      </c>
+      <c r="V41" s="42">
+        <f t="shared" si="7"/>
+        <v>57.08</v>
+      </c>
+      <c r="W41" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="X41" s="3">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A42" s="36">
+        <v>65429</v>
+      </c>
+      <c r="B42" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="C42" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="F42" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="G42" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="H42" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="I42" s="40">
+        <v>46235</v>
+      </c>
+      <c r="J42" s="41">
+        <v>6.66</v>
+      </c>
+      <c r="K42" s="41">
+        <v>50813.96469999999</v>
+      </c>
+      <c r="L42" s="41">
+        <v>6.66</v>
+      </c>
+      <c r="M42" s="41">
+        <v>50813.96469999999</v>
+      </c>
+      <c r="N42" s="41">
+        <v>5.12</v>
+      </c>
+      <c r="O42" s="41">
+        <v>50813.96469999999</v>
+      </c>
+      <c r="P42" s="41">
+        <v>5.12</v>
+      </c>
+      <c r="Q42" s="41">
+        <v>50813.96469999999</v>
+      </c>
+      <c r="R42" s="41">
+        <v>0</v>
+      </c>
+      <c r="S42" s="41">
+        <v>0</v>
+      </c>
+      <c r="T42" s="41">
+        <v>0</v>
+      </c>
+      <c r="U42" s="41">
+        <v>0</v>
+      </c>
+      <c r="V42" s="42">
+        <f t="shared" si="7"/>
+        <v>23.560000000000002</v>
+      </c>
+      <c r="W42" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="X42" s="3">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A43" s="36">
+        <v>65431</v>
+      </c>
+      <c r="B43" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="C43" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="D43" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="F43" s="44" t="s">
+        <v>116</v>
+      </c>
+      <c r="G43" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="H43" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="I43" s="45">
+        <v>46235</v>
+      </c>
+      <c r="J43" s="46">
+        <v>56.95</v>
+      </c>
+      <c r="K43" s="46">
+        <v>174920.42099999997</v>
+      </c>
+      <c r="L43" s="46">
+        <v>56.95</v>
+      </c>
+      <c r="M43" s="46">
+        <v>174920.42099999997</v>
+      </c>
+      <c r="N43" s="46">
+        <v>29.56</v>
+      </c>
+      <c r="O43" s="46">
+        <v>174920.42099999997</v>
+      </c>
+      <c r="P43" s="46">
+        <v>29.56</v>
+      </c>
+      <c r="Q43" s="46">
+        <v>174920.42099999997</v>
+      </c>
+      <c r="R43" s="46">
+        <v>0</v>
+      </c>
+      <c r="S43" s="46">
+        <v>0</v>
+      </c>
+      <c r="T43" s="46">
+        <v>0</v>
+      </c>
+      <c r="U43" s="46">
+        <v>0</v>
+      </c>
+      <c r="V43" s="47">
+        <f>SUM(T43,R43,P43,N43,L43,J43)</f>
+        <v>173.01999999999998</v>
+      </c>
+      <c r="W43" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="X43" s="3">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A44" s="36">
+        <v>65432</v>
+      </c>
+      <c r="B44" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="D44" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="F44" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="G44" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="H44" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="I44" s="45">
+        <v>46235</v>
+      </c>
+      <c r="J44" s="46">
+        <v>45.56</v>
+      </c>
+      <c r="K44" s="46">
+        <v>236948.35645000002</v>
+      </c>
+      <c r="L44" s="46">
+        <v>45.56</v>
+      </c>
+      <c r="M44" s="46">
+        <v>236948.35645000002</v>
+      </c>
+      <c r="N44" s="46">
+        <v>30.17</v>
+      </c>
+      <c r="O44" s="46">
+        <v>236948.35645000002</v>
+      </c>
+      <c r="P44" s="46">
+        <v>30.17</v>
+      </c>
+      <c r="Q44" s="46">
+        <v>236948.35645000002</v>
+      </c>
+      <c r="R44" s="46">
+        <v>0</v>
+      </c>
+      <c r="S44" s="46">
+        <v>0</v>
+      </c>
+      <c r="T44" s="46">
+        <v>0</v>
+      </c>
+      <c r="U44" s="46">
+        <v>0</v>
+      </c>
+      <c r="V44" s="47">
+        <f t="shared" ref="V44" si="8">SUM(T44,R44,P44,N44,L44,J44)</f>
+        <v>151.46</v>
+      </c>
+      <c r="W44" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="X44" s="3">
+        <v>46267</v>
       </c>
     </row>
   </sheetData>

--- a/RELACAO DE MALOTE RECEBIDO SEGURADORA.xlsx
+++ b/RELACAO DE MALOTE RECEBIDO SEGURADORA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974212F6-4BB1-41F0-805B-C16E683E27E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35DC9DF-3BB4-439F-8C6C-B945E728076D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5A1C727-9BF2-4FA6-AD32-FEB667895D86}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="120">
   <si>
     <t>TIPO</t>
   </si>
@@ -560,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -605,7 +605,6 @@
     <xf numFmtId="17" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1042,7 +1041,7 @@
     <col min="1" max="1" width="6.75" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="20.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38" style="35" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38" style="34" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40.25" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.25" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="53" style="1" bestFit="1" customWidth="1"/>
@@ -1140,74 +1139,74 @@
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="19">
+      <c r="A2" s="18">
         <v>53946</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="20">
         <v>115935528</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="22" t="s">
+      <c r="D2" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="23">
+      <c r="I2" s="22">
         <v>46235</v>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="23">
         <v>6.62</v>
       </c>
-      <c r="K2" s="24">
+      <c r="K2" s="23">
         <v>20319.400000000001</v>
       </c>
-      <c r="L2" s="24">
+      <c r="L2" s="23">
         <v>6.62</v>
       </c>
-      <c r="M2" s="24">
+      <c r="M2" s="23">
         <v>20319.400000000001</v>
       </c>
-      <c r="N2" s="24">
+      <c r="N2" s="23">
         <v>3.43</v>
       </c>
-      <c r="O2" s="24">
+      <c r="O2" s="23">
         <v>20319.400000000001</v>
       </c>
-      <c r="P2" s="24">
+      <c r="P2" s="23">
         <v>3.43</v>
       </c>
-      <c r="Q2" s="24">
+      <c r="Q2" s="23">
         <v>20319.400000000001</v>
       </c>
-      <c r="R2" s="24">
-        <v>0</v>
-      </c>
-      <c r="S2" s="24">
-        <v>0</v>
-      </c>
-      <c r="T2" s="24">
+      <c r="R2" s="23">
+        <v>0</v>
+      </c>
+      <c r="S2" s="23">
+        <v>0</v>
+      </c>
+      <c r="T2" s="23">
         <v>50</v>
       </c>
-      <c r="U2" s="24">
+      <c r="U2" s="23">
         <v>295857.99</v>
       </c>
-      <c r="V2" s="25">
+      <c r="V2" s="24">
         <f>SUM(J2,L2,N2,P2,R2,T2)</f>
         <v>70.099999999999994</v>
       </c>
-      <c r="W2" s="24" t="s">
+      <c r="W2" s="23" t="s">
         <v>9</v>
       </c>
       <c r="X2" s="3">
@@ -1218,74 +1217,74 @@
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="19">
+      <c r="A3" s="18">
         <v>62590</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="20">
         <v>115937631</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="22" t="s">
+      <c r="D3" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="22">
         <v>46235</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="23">
         <v>140.44</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="23">
         <v>431385.89</v>
       </c>
-      <c r="L3" s="24">
+      <c r="L3" s="23">
         <v>140.44</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="23">
         <v>431385.89</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="23">
         <v>72.900000000000006</v>
       </c>
-      <c r="O3" s="24">
+      <c r="O3" s="23">
         <v>431385.89</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="23">
         <v>72.900000000000006</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="23">
         <v>431385.89</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="23">
         <v>200</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="23">
         <v>614326.07999999996</v>
       </c>
-      <c r="T3" s="24">
+      <c r="T3" s="23">
         <v>100</v>
       </c>
-      <c r="U3" s="24">
+      <c r="U3" s="23">
         <v>591715.98</v>
       </c>
-      <c r="V3" s="25">
+      <c r="V3" s="24">
         <f t="shared" ref="V3:V5" si="0">SUM(J3,L3,N3,P3,R3,T3)</f>
         <v>726.68</v>
       </c>
-      <c r="W3" s="24" t="s">
+      <c r="W3" s="23" t="s">
         <v>9</v>
       </c>
       <c r="X3" s="3">
@@ -1293,74 +1292,74 @@
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="19">
+      <c r="A4" s="18">
         <v>55064</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="20">
         <v>115937636</v>
       </c>
-      <c r="D4" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="22" t="s">
+      <c r="D4" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="23">
+      <c r="I4" s="22">
         <v>46235</v>
       </c>
-      <c r="J4" s="24">
+      <c r="J4" s="23">
         <v>52.87</v>
       </c>
-      <c r="K4" s="24">
+      <c r="K4" s="23">
         <v>274950.17</v>
       </c>
-      <c r="L4" s="24">
+      <c r="L4" s="23">
         <v>52.87</v>
       </c>
-      <c r="M4" s="24">
+      <c r="M4" s="23">
         <v>274950.17</v>
       </c>
-      <c r="N4" s="24">
+      <c r="N4" s="23">
         <v>35.01</v>
       </c>
-      <c r="O4" s="24">
+      <c r="O4" s="23">
         <v>274950.17</v>
       </c>
-      <c r="P4" s="24">
+      <c r="P4" s="23">
         <v>35.01</v>
       </c>
-      <c r="Q4" s="24">
+      <c r="Q4" s="23">
         <v>274950.17</v>
       </c>
-      <c r="R4" s="24">
-        <v>0</v>
-      </c>
-      <c r="S4" s="24">
-        <v>0</v>
-      </c>
-      <c r="T4" s="24">
+      <c r="R4" s="23">
+        <v>0</v>
+      </c>
+      <c r="S4" s="23">
+        <v>0</v>
+      </c>
+      <c r="T4" s="23">
         <v>400</v>
       </c>
-      <c r="U4" s="24">
+      <c r="U4" s="23">
         <v>3141369.48</v>
       </c>
-      <c r="V4" s="25">
+      <c r="V4" s="24">
         <f t="shared" si="0"/>
         <v>575.76</v>
       </c>
-      <c r="W4" s="27" t="s">
+      <c r="W4" s="26" t="s">
         <v>9</v>
       </c>
       <c r="X4" s="3">
@@ -1368,74 +1367,74 @@
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A5" s="19">
+      <c r="A5" s="18">
         <v>55054</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="20">
         <v>115937635</v>
       </c>
-      <c r="D5" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="22" t="s">
+      <c r="D5" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="H5" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="22">
         <v>46235</v>
       </c>
-      <c r="J5" s="24">
+      <c r="J5" s="23">
         <v>50.22</v>
       </c>
-      <c r="K5" s="24">
+      <c r="K5" s="23">
         <v>261159.56</v>
       </c>
-      <c r="L5" s="24">
+      <c r="L5" s="23">
         <v>50.22</v>
       </c>
-      <c r="M5" s="24">
+      <c r="M5" s="23">
         <v>261159.56</v>
       </c>
-      <c r="N5" s="24">
+      <c r="N5" s="23">
         <v>33.25</v>
       </c>
-      <c r="O5" s="24">
+      <c r="O5" s="23">
         <v>261159.56</v>
       </c>
-      <c r="P5" s="24">
+      <c r="P5" s="23">
         <v>33.25</v>
       </c>
-      <c r="Q5" s="24">
+      <c r="Q5" s="23">
         <v>261159.56</v>
       </c>
-      <c r="R5" s="24">
-        <v>0</v>
-      </c>
-      <c r="S5" s="24">
-        <v>0</v>
-      </c>
-      <c r="T5" s="24">
-        <v>0</v>
-      </c>
-      <c r="U5" s="24">
-        <v>0</v>
-      </c>
-      <c r="V5" s="25">
+      <c r="R5" s="23">
+        <v>0</v>
+      </c>
+      <c r="S5" s="23">
+        <v>0</v>
+      </c>
+      <c r="T5" s="23">
+        <v>0</v>
+      </c>
+      <c r="U5" s="23">
+        <v>0</v>
+      </c>
+      <c r="V5" s="24">
         <f t="shared" si="0"/>
         <v>166.94</v>
       </c>
-      <c r="W5" s="27" t="s">
+      <c r="W5" s="26" t="s">
         <v>9</v>
       </c>
       <c r="X5" s="3">
@@ -1443,74 +1442,74 @@
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>62592</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="18">
         <v>115937633</v>
       </c>
-      <c r="D6" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="33" t="s">
+      <c r="D6" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="28" t="s">
+      <c r="G6" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="H6" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="29">
+      <c r="I6" s="28">
         <v>46235</v>
       </c>
-      <c r="J6" s="30">
+      <c r="J6" s="29">
         <v>181.54</v>
       </c>
-      <c r="K6" s="30">
+      <c r="K6" s="29">
         <v>557631.23</v>
       </c>
-      <c r="L6" s="30">
+      <c r="L6" s="29">
         <v>181.54</v>
       </c>
-      <c r="M6" s="30">
+      <c r="M6" s="29">
         <v>557631.23</v>
       </c>
-      <c r="N6" s="30">
+      <c r="N6" s="29">
         <v>94.24</v>
       </c>
-      <c r="O6" s="30">
+      <c r="O6" s="29">
         <v>557631.23</v>
       </c>
-      <c r="P6" s="30">
+      <c r="P6" s="29">
         <v>94.24</v>
       </c>
-      <c r="Q6" s="30">
+      <c r="Q6" s="29">
         <v>557631.23</v>
       </c>
-      <c r="R6" s="30">
-        <v>0</v>
-      </c>
-      <c r="S6" s="30">
-        <v>0</v>
-      </c>
-      <c r="T6" s="30">
+      <c r="R6" s="29">
+        <v>0</v>
+      </c>
+      <c r="S6" s="29">
+        <v>0</v>
+      </c>
+      <c r="T6" s="29">
         <v>300</v>
       </c>
-      <c r="U6" s="30">
+      <c r="U6" s="29">
         <v>1775147.93</v>
       </c>
-      <c r="V6" s="31">
+      <c r="V6" s="30">
         <f>SUM(T6,R6,P6,N6,L6,J6)</f>
         <v>851.56</v>
       </c>
-      <c r="W6" s="30" t="s">
+      <c r="W6" s="29" t="s">
         <v>9</v>
       </c>
       <c r="X6" s="3">
@@ -1518,74 +1517,74 @@
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A7" s="19">
+      <c r="A7" s="18">
         <v>62596</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="18">
         <v>115937634</v>
       </c>
-      <c r="D7" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="33" t="s">
+      <c r="D7" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="G7" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="28">
         <v>46235</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="29">
         <v>241.41</v>
       </c>
-      <c r="K7" s="30">
+      <c r="K7" s="29">
         <v>741534.7</v>
       </c>
-      <c r="L7" s="30">
+      <c r="L7" s="29">
         <v>241.41</v>
       </c>
-      <c r="M7" s="30">
+      <c r="M7" s="29">
         <v>741534.7</v>
       </c>
-      <c r="N7" s="30">
+      <c r="N7" s="29">
         <v>125.32</v>
       </c>
-      <c r="O7" s="30">
+      <c r="O7" s="29">
         <v>741534.7</v>
       </c>
-      <c r="P7" s="30">
+      <c r="P7" s="29">
         <v>125.32</v>
       </c>
-      <c r="Q7" s="30">
+      <c r="Q7" s="29">
         <v>741534.7</v>
       </c>
-      <c r="R7" s="30">
+      <c r="R7" s="29">
         <v>100</v>
       </c>
-      <c r="S7" s="30">
+      <c r="S7" s="29">
         <v>307163.03999999998</v>
       </c>
-      <c r="T7" s="30">
+      <c r="T7" s="29">
         <v>150</v>
       </c>
-      <c r="U7" s="30">
+      <c r="U7" s="29">
         <v>887573.96</v>
       </c>
-      <c r="V7" s="31">
+      <c r="V7" s="30">
         <f t="shared" ref="V7:V15" si="1">SUM(T7,R7,P7,N7,L7,J7)</f>
         <v>983.45999999999992</v>
       </c>
-      <c r="W7" s="30" t="s">
+      <c r="W7" s="29" t="s">
         <v>9</v>
       </c>
       <c r="X7" s="3">
@@ -1593,74 +1592,74 @@
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="19">
+      <c r="A8" s="18">
         <v>56516</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="18">
         <v>115937638</v>
       </c>
-      <c r="D8" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="33" t="s">
+      <c r="D8" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="28" t="s">
+      <c r="G8" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="28" t="s">
+      <c r="H8" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="28">
         <v>46235</v>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="29">
         <v>42.23</v>
       </c>
-      <c r="K8" s="30">
+      <c r="K8" s="29">
         <v>322355.37</v>
       </c>
-      <c r="L8" s="30">
+      <c r="L8" s="29">
         <v>42.23</v>
       </c>
-      <c r="M8" s="30">
+      <c r="M8" s="29">
         <v>322355.37</v>
       </c>
-      <c r="N8" s="30">
+      <c r="N8" s="29">
         <v>32.5</v>
       </c>
-      <c r="O8" s="30">
+      <c r="O8" s="29">
         <v>322355.37</v>
       </c>
-      <c r="P8" s="30">
+      <c r="P8" s="29">
         <v>32.5</v>
       </c>
-      <c r="Q8" s="30">
+      <c r="Q8" s="29">
         <v>322355.37</v>
       </c>
-      <c r="R8" s="30">
-        <v>0</v>
-      </c>
-      <c r="S8" s="30">
-        <v>0</v>
-      </c>
-      <c r="T8" s="30">
-        <v>0</v>
-      </c>
-      <c r="U8" s="30">
-        <v>0</v>
-      </c>
-      <c r="V8" s="31">
+      <c r="R8" s="29">
+        <v>0</v>
+      </c>
+      <c r="S8" s="29">
+        <v>0</v>
+      </c>
+      <c r="T8" s="29">
+        <v>0</v>
+      </c>
+      <c r="U8" s="29">
+        <v>0</v>
+      </c>
+      <c r="V8" s="30">
         <f t="shared" si="1"/>
         <v>149.45999999999998</v>
       </c>
-      <c r="W8" s="19" t="s">
+      <c r="W8" s="18" t="s">
         <v>9</v>
       </c>
       <c r="X8" s="3">
@@ -1668,74 +1667,74 @@
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A9" s="19">
+      <c r="A9" s="18">
         <v>62594</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="18">
         <v>115937639</v>
       </c>
-      <c r="D9" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="33" t="s">
+      <c r="D9" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="28" t="s">
+      <c r="G9" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="H9" s="28" t="s">
+      <c r="H9" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="29">
+      <c r="I9" s="28">
         <v>46235</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="29">
         <v>58.54</v>
       </c>
-      <c r="K9" s="30">
+      <c r="K9" s="29">
         <v>304424.75</v>
       </c>
-      <c r="L9" s="30">
+      <c r="L9" s="29">
         <v>58.54</v>
       </c>
-      <c r="M9" s="30">
+      <c r="M9" s="29">
         <v>304424.75</v>
       </c>
-      <c r="N9" s="30">
+      <c r="N9" s="29">
         <v>38.76</v>
       </c>
-      <c r="O9" s="30">
+      <c r="O9" s="29">
         <v>304424.75</v>
       </c>
-      <c r="P9" s="30">
+      <c r="P9" s="29">
         <v>38.76</v>
       </c>
-      <c r="Q9" s="30">
+      <c r="Q9" s="29">
         <v>304424.75</v>
       </c>
-      <c r="R9" s="30">
+      <c r="R9" s="29">
         <v>175</v>
       </c>
-      <c r="S9" s="30">
+      <c r="S9" s="29">
         <v>910045.87</v>
       </c>
-      <c r="T9" s="30">
+      <c r="T9" s="29">
         <v>125</v>
       </c>
-      <c r="U9" s="30">
+      <c r="U9" s="29">
         <v>981677.96</v>
       </c>
-      <c r="V9" s="31">
+      <c r="V9" s="30">
         <f t="shared" si="1"/>
         <v>494.6</v>
       </c>
-      <c r="W9" s="19" t="s">
+      <c r="W9" s="18" t="s">
         <v>9</v>
       </c>
       <c r="X9" s="3">
@@ -1743,74 +1742,74 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A10" s="19">
+      <c r="A10" s="18">
         <v>54015</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="18">
         <v>115971164</v>
       </c>
-      <c r="D10" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="33" t="s">
+      <c r="D10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="28" t="s">
+      <c r="G10" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="28" t="s">
+      <c r="H10" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="I10" s="29">
+      <c r="I10" s="28">
         <v>46235</v>
       </c>
-      <c r="J10" s="30">
+      <c r="J10" s="29">
         <v>37.090000000000003</v>
       </c>
-      <c r="K10" s="30">
+      <c r="K10" s="29">
         <v>113915.44</v>
       </c>
-      <c r="L10" s="30">
+      <c r="L10" s="29">
         <v>37.090000000000003</v>
       </c>
-      <c r="M10" s="30">
+      <c r="M10" s="29">
         <v>113915.44</v>
       </c>
-      <c r="N10" s="30">
+      <c r="N10" s="29">
         <v>19.25</v>
       </c>
-      <c r="O10" s="30">
+      <c r="O10" s="29">
         <v>113915.44</v>
       </c>
-      <c r="P10" s="30">
+      <c r="P10" s="29">
         <v>19.25</v>
       </c>
-      <c r="Q10" s="30">
+      <c r="Q10" s="29">
         <v>113915.44</v>
       </c>
-      <c r="R10" s="30">
-        <v>0</v>
-      </c>
-      <c r="S10" s="30">
-        <v>0</v>
-      </c>
-      <c r="T10" s="30">
-        <v>0</v>
-      </c>
-      <c r="U10" s="30">
-        <v>0</v>
-      </c>
-      <c r="V10" s="31">
+      <c r="R10" s="29">
+        <v>0</v>
+      </c>
+      <c r="S10" s="29">
+        <v>0</v>
+      </c>
+      <c r="T10" s="29">
+        <v>0</v>
+      </c>
+      <c r="U10" s="29">
+        <v>0</v>
+      </c>
+      <c r="V10" s="30">
         <f t="shared" si="1"/>
         <v>112.68</v>
       </c>
-      <c r="W10" s="30" t="s">
+      <c r="W10" s="29" t="s">
         <v>9</v>
       </c>
       <c r="X10" s="3">
@@ -1818,74 +1817,74 @@
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A11" s="19">
+      <c r="A11" s="18">
         <v>54059</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="18">
         <v>115971165</v>
       </c>
-      <c r="D11" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="33" t="s">
+      <c r="D11" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="28" t="s">
+      <c r="G11" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="H11" s="28" t="s">
+      <c r="H11" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="I11" s="29">
+      <c r="I11" s="28">
         <v>46235</v>
       </c>
-      <c r="J11" s="30">
+      <c r="J11" s="29">
         <v>26.45</v>
       </c>
-      <c r="K11" s="30">
+      <c r="K11" s="29">
         <v>137571.42000000001</v>
       </c>
-      <c r="L11" s="30">
+      <c r="L11" s="29">
         <v>26.45</v>
       </c>
-      <c r="M11" s="30">
+      <c r="M11" s="29">
         <v>137571.42000000001</v>
       </c>
-      <c r="N11" s="30">
+      <c r="N11" s="29">
         <v>17.52</v>
       </c>
-      <c r="O11" s="30">
+      <c r="O11" s="29">
         <v>137571.42000000001</v>
       </c>
-      <c r="P11" s="30">
+      <c r="P11" s="29">
         <v>17.52</v>
       </c>
-      <c r="Q11" s="30">
+      <c r="Q11" s="29">
         <v>137571.42000000001</v>
       </c>
-      <c r="R11" s="30">
+      <c r="R11" s="29">
         <v>35</v>
       </c>
-      <c r="S11" s="30">
+      <c r="S11" s="29">
         <v>182009.17</v>
       </c>
-      <c r="T11" s="30">
+      <c r="T11" s="29">
         <v>35</v>
       </c>
-      <c r="U11" s="30">
+      <c r="U11" s="29">
         <v>274869.83</v>
       </c>
-      <c r="V11" s="31">
+      <c r="V11" s="30">
         <f t="shared" si="1"/>
         <v>157.93999999999997</v>
       </c>
-      <c r="W11" s="30" t="s">
+      <c r="W11" s="29" t="s">
         <v>9</v>
       </c>
       <c r="X11" s="3">
@@ -1893,74 +1892,74 @@
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="19">
+      <c r="A12" s="18">
         <v>54055</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="18">
         <v>115971166</v>
       </c>
-      <c r="D12" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="33" t="s">
+      <c r="D12" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="28" t="s">
+      <c r="G12" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="H12" s="28" t="s">
+      <c r="H12" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="I12" s="29">
+      <c r="I12" s="28">
         <v>46235</v>
       </c>
-      <c r="J12" s="30">
+      <c r="J12" s="29">
         <v>34.04</v>
       </c>
-      <c r="K12" s="30">
+      <c r="K12" s="29">
         <v>177018.17</v>
       </c>
-      <c r="L12" s="30">
+      <c r="L12" s="29">
         <v>34.04</v>
       </c>
-      <c r="M12" s="30">
+      <c r="M12" s="29">
         <v>177018.17</v>
       </c>
-      <c r="N12" s="30">
+      <c r="N12" s="29">
         <v>22.54</v>
       </c>
-      <c r="O12" s="30">
+      <c r="O12" s="29">
         <v>177018.17</v>
       </c>
-      <c r="P12" s="30">
+      <c r="P12" s="29">
         <v>22.54</v>
       </c>
-      <c r="Q12" s="30">
+      <c r="Q12" s="29">
         <v>177018.17</v>
       </c>
-      <c r="R12" s="30">
+      <c r="R12" s="29">
         <v>50</v>
       </c>
-      <c r="S12" s="30">
+      <c r="S12" s="29">
         <v>260013.1</v>
       </c>
-      <c r="T12" s="30">
+      <c r="T12" s="29">
         <v>50</v>
       </c>
-      <c r="U12" s="30">
+      <c r="U12" s="29">
         <v>392671.19</v>
       </c>
-      <c r="V12" s="31">
+      <c r="V12" s="30">
         <f t="shared" si="1"/>
         <v>213.15999999999997</v>
       </c>
-      <c r="W12" s="19" t="s">
+      <c r="W12" s="18" t="s">
         <v>9</v>
       </c>
       <c r="X12" s="3">
@@ -1968,74 +1967,74 @@
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="19">
+      <c r="A13" s="18">
         <v>64986</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="18">
         <v>115937643</v>
       </c>
-      <c r="D13" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="33" t="s">
+      <c r="D13" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="G13" s="28" t="s">
+      <c r="G13" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="28" t="s">
+      <c r="H13" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="I13" s="29">
+      <c r="I13" s="28">
         <v>46235</v>
       </c>
-      <c r="J13" s="30">
+      <c r="J13" s="29">
         <v>157.27000000000001</v>
       </c>
-      <c r="K13" s="30">
+      <c r="K13" s="29">
         <v>817869.15</v>
       </c>
-      <c r="L13" s="30">
+      <c r="L13" s="29">
         <v>157.27000000000001</v>
       </c>
-      <c r="M13" s="30">
+      <c r="M13" s="29">
         <v>817869.15</v>
       </c>
-      <c r="N13" s="30">
+      <c r="N13" s="29">
         <v>104.14</v>
       </c>
-      <c r="O13" s="30">
+      <c r="O13" s="29">
         <v>817869.15</v>
       </c>
-      <c r="P13" s="30">
+      <c r="P13" s="29">
         <v>104.14</v>
       </c>
-      <c r="Q13" s="30">
+      <c r="Q13" s="29">
         <v>817869.15</v>
       </c>
-      <c r="R13" s="30">
+      <c r="R13" s="29">
         <v>600</v>
       </c>
-      <c r="S13" s="30">
+      <c r="S13" s="29">
         <v>3120157.26</v>
       </c>
-      <c r="T13" s="30">
+      <c r="T13" s="29">
         <v>550</v>
       </c>
-      <c r="U13" s="30">
+      <c r="U13" s="29">
         <v>4319383.04</v>
       </c>
-      <c r="V13" s="31">
+      <c r="V13" s="30">
         <f t="shared" si="1"/>
         <v>1672.8200000000002</v>
       </c>
-      <c r="W13" s="19" t="s">
+      <c r="W13" s="18" t="s">
         <v>9</v>
       </c>
       <c r="X13" s="3">
@@ -2055,7 +2054,7 @@
       <c r="D14" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="34" t="s">
+      <c r="E14" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F14" s="9" t="s">
@@ -2130,7 +2129,7 @@
       <c r="D15" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="34" t="s">
+      <c r="E15" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F15" s="9" t="s">
@@ -2205,7 +2204,7 @@
       <c r="D16" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="34" t="s">
+      <c r="E16" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F16" s="9" t="s">
@@ -2258,8 +2257,10 @@
         <f t="shared" ref="V16:V22" si="2">SUM(T16,R16,P16,N16,L16,J16)</f>
         <v>439.4</v>
       </c>
-      <c r="W16" s="16"/>
-      <c r="X16" s="17">
+      <c r="W16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X16" s="16">
         <v>46241</v>
       </c>
     </row>
@@ -2276,7 +2277,7 @@
       <c r="D17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="E17" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F17" s="9" t="s">
@@ -2315,24 +2316,26 @@
       <c r="Q17" s="5">
         <v>317460.47999999998</v>
       </c>
-      <c r="R17" s="18">
-        <v>0</v>
-      </c>
-      <c r="S17" s="18">
-        <v>0</v>
-      </c>
-      <c r="T17" s="18">
-        <v>0</v>
-      </c>
-      <c r="U17" s="18">
+      <c r="R17" s="17">
+        <v>0</v>
+      </c>
+      <c r="S17" s="17">
+        <v>0</v>
+      </c>
+      <c r="T17" s="17">
+        <v>0</v>
+      </c>
+      <c r="U17" s="17">
         <v>0</v>
       </c>
       <c r="V17" s="14">
         <f t="shared" si="2"/>
         <v>147.19999999999999</v>
       </c>
-      <c r="W17" s="16"/>
-      <c r="X17" s="17">
+      <c r="W17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X17" s="16">
         <v>46241</v>
       </c>
     </row>
@@ -2349,7 +2352,7 @@
       <c r="D18" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F18" s="9" t="s">
@@ -2402,8 +2405,10 @@
         <f t="shared" si="2"/>
         <v>49.96</v>
       </c>
-      <c r="W18" s="16"/>
-      <c r="X18" s="17">
+      <c r="W18" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X18" s="16">
         <v>46241</v>
       </c>
     </row>
@@ -2420,7 +2425,7 @@
       <c r="D19" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="E19" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F19" s="9" t="s">
@@ -2475,8 +2480,10 @@
         <f t="shared" si="2"/>
         <v>118.27999999999999</v>
       </c>
-      <c r="W19" s="16"/>
-      <c r="X19" s="17">
+      <c r="W19" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X19" s="16">
         <v>46241</v>
       </c>
     </row>
@@ -2493,7 +2500,7 @@
       <c r="D20" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="34" t="s">
+      <c r="E20" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F20" s="9" t="s">
@@ -2548,8 +2555,10 @@
         <f t="shared" si="2"/>
         <v>125.4</v>
       </c>
-      <c r="W20" s="16"/>
-      <c r="X20" s="17">
+      <c r="W20" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X20" s="16">
         <v>46241</v>
       </c>
     </row>
@@ -2566,7 +2575,7 @@
       <c r="D21" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="34" t="s">
+      <c r="E21" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F21" s="9" t="s">
@@ -2619,8 +2628,10 @@
         <f t="shared" si="2"/>
         <v>324.52</v>
       </c>
-      <c r="W21" s="16"/>
-      <c r="X21" s="17">
+      <c r="W21" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X21" s="16">
         <v>46241</v>
       </c>
     </row>
@@ -2637,7 +2648,7 @@
       <c r="D22" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="34" t="s">
+      <c r="E22" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F22" s="9" t="s">
@@ -2685,15 +2696,17 @@
       <c r="T22" s="5">
         <v>0</v>
       </c>
-      <c r="U22" s="18">
+      <c r="U22" s="17">
         <v>0</v>
       </c>
       <c r="V22" s="14">
         <f t="shared" si="2"/>
         <v>101.62</v>
       </c>
-      <c r="W22" s="16"/>
-      <c r="X22" s="17">
+      <c r="W22" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X22" s="16">
         <v>46241</v>
       </c>
     </row>
@@ -2710,7 +2723,7 @@
       <c r="D23" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="34" t="s">
+      <c r="E23" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F23" s="9" t="s">
@@ -2765,8 +2778,10 @@
         <f t="shared" ref="V23:V25" si="3">SUM(T23,R23,P23,N23,L23,J23)</f>
         <v>18.68</v>
       </c>
-      <c r="W23" s="16"/>
-      <c r="X23" s="17">
+      <c r="W23" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X23" s="16">
         <v>46251</v>
       </c>
     </row>
@@ -2783,7 +2798,7 @@
       <c r="D24" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="34" t="s">
+      <c r="E24" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F24" s="9" t="s">
@@ -2838,8 +2853,10 @@
         <f t="shared" si="3"/>
         <v>176.68</v>
       </c>
-      <c r="W24" s="16"/>
-      <c r="X24" s="17">
+      <c r="W24" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X24" s="16">
         <v>46251</v>
       </c>
     </row>
@@ -2856,7 +2873,7 @@
       <c r="D25" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="34" t="s">
+      <c r="E25" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F25" s="9" t="s">
@@ -2904,15 +2921,17 @@
       <c r="T25" s="5">
         <v>0</v>
       </c>
-      <c r="U25" s="18">
+      <c r="U25" s="17">
         <v>0</v>
       </c>
       <c r="V25" s="14">
         <f t="shared" si="3"/>
         <v>94.58</v>
       </c>
-      <c r="W25" s="16"/>
-      <c r="X25" s="17">
+      <c r="W25" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X25" s="16">
         <v>46251</v>
       </c>
     </row>
@@ -2929,7 +2948,7 @@
       <c r="D26" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="34" t="s">
+      <c r="E26" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F26" s="9" t="s">
@@ -2984,8 +3003,10 @@
         <f t="shared" ref="V26:V28" si="4">SUM(T26,R26,P26,N26,L26,J26)</f>
         <v>115.28</v>
       </c>
-      <c r="W26" s="16"/>
-      <c r="X26" s="17">
+      <c r="W26" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X26" s="16">
         <v>46255</v>
       </c>
     </row>
@@ -3002,7 +3023,7 @@
       <c r="D27" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="34" t="s">
+      <c r="E27" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F27" s="9" t="s">
@@ -3057,8 +3078,10 @@
         <f t="shared" si="4"/>
         <v>453.14</v>
       </c>
-      <c r="W27" s="16"/>
-      <c r="X27" s="17">
+      <c r="W27" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X27" s="16">
         <v>46255</v>
       </c>
     </row>
@@ -3075,7 +3098,7 @@
       <c r="D28" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="34" t="s">
+      <c r="E28" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F28" s="9" t="s">
@@ -3123,15 +3146,17 @@
       <c r="T28" s="5">
         <v>0</v>
       </c>
-      <c r="U28" s="18">
+      <c r="U28" s="17">
         <v>0</v>
       </c>
       <c r="V28" s="14">
         <f t="shared" si="4"/>
         <v>139.98000000000002</v>
       </c>
-      <c r="W28" s="16"/>
-      <c r="X28" s="17">
+      <c r="W28" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X28" s="16">
         <v>46255</v>
       </c>
     </row>
@@ -3148,7 +3173,7 @@
       <c r="D29" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="34" t="s">
+      <c r="E29" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F29" s="9" t="s">
@@ -3203,11 +3228,13 @@
         <f t="shared" ref="V29:V34" si="5">SUM(T29,R29,P29,N29,L29,J29)</f>
         <v>112.78</v>
       </c>
-      <c r="W29" s="16"/>
-      <c r="X29" s="17">
+      <c r="W29" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X29" s="16">
         <v>46259</v>
       </c>
-      <c r="Y29" s="32" t="s">
+      <c r="Y29" s="31" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3224,7 +3251,7 @@
       <c r="D30" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E30" s="34" t="s">
+      <c r="E30" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F30" s="9" t="s">
@@ -3279,8 +3306,10 @@
         <f t="shared" si="5"/>
         <v>105.88</v>
       </c>
-      <c r="W30" s="16"/>
-      <c r="X30" s="17">
+      <c r="W30" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X30" s="16">
         <v>46259</v>
       </c>
     </row>
@@ -3297,7 +3326,7 @@
       <c r="D31" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E31" s="34" t="s">
+      <c r="E31" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F31" s="9" t="s">
@@ -3345,15 +3374,17 @@
       <c r="T31" s="5">
         <v>0</v>
       </c>
-      <c r="U31" s="18">
+      <c r="U31" s="17">
         <v>0</v>
       </c>
       <c r="V31" s="14">
         <f t="shared" si="5"/>
         <v>165.51999999999998</v>
       </c>
-      <c r="W31" s="16"/>
-      <c r="X31" s="17">
+      <c r="W31" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X31" s="16">
         <v>46259</v>
       </c>
     </row>
@@ -3370,7 +3401,7 @@
       <c r="D32" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="34" t="s">
+      <c r="E32" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F32" s="9" t="s">
@@ -3425,8 +3456,10 @@
         <f t="shared" si="5"/>
         <v>251.64</v>
       </c>
-      <c r="W32" s="16"/>
-      <c r="X32" s="17">
+      <c r="W32" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X32" s="16">
         <v>46259</v>
       </c>
     </row>
@@ -3443,7 +3476,7 @@
       <c r="D33" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E33" s="34" t="s">
+      <c r="E33" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F33" s="9" t="s">
@@ -3498,8 +3531,10 @@
         <f t="shared" si="5"/>
         <v>240.26</v>
       </c>
-      <c r="W33" s="16"/>
-      <c r="X33" s="17">
+      <c r="W33" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X33" s="16">
         <v>46259</v>
       </c>
     </row>
@@ -3516,7 +3551,7 @@
       <c r="D34" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E34" s="34" t="s">
+      <c r="E34" s="33" t="s">
         <v>10</v>
       </c>
       <c r="F34" s="9" t="s">
@@ -3564,15 +3599,17 @@
       <c r="T34" s="5">
         <v>0</v>
       </c>
-      <c r="U34" s="18">
+      <c r="U34" s="17">
         <v>0</v>
       </c>
       <c r="V34" s="14">
         <f t="shared" si="5"/>
         <v>210.16</v>
       </c>
-      <c r="W34" s="16"/>
-      <c r="X34" s="17">
+      <c r="W34" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X34" s="16">
         <v>46259</v>
       </c>
     </row>
@@ -3589,7 +3626,7 @@
       <c r="D35" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E35" s="34" t="s">
+      <c r="E35" s="33" t="s">
         <v>98</v>
       </c>
       <c r="F35" s="9" t="s">
@@ -3644,8 +3681,10 @@
         <f t="shared" ref="V35:V38" si="6">SUM(T35,R35,P35,N35,L35,J35)</f>
         <v>296.56</v>
       </c>
-      <c r="W35" s="16"/>
-      <c r="X35" s="17">
+      <c r="W35" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X35" s="16">
         <v>46262</v>
       </c>
     </row>
@@ -3662,7 +3701,7 @@
       <c r="D36" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E36" s="34" t="s">
+      <c r="E36" s="33" t="s">
         <v>98</v>
       </c>
       <c r="F36" s="9" t="s">
@@ -3717,8 +3756,10 @@
         <f t="shared" si="6"/>
         <v>3.46</v>
       </c>
-      <c r="W36" s="16"/>
-      <c r="X36" s="17">
+      <c r="W36" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X36" s="16">
         <v>46262</v>
       </c>
     </row>
@@ -3735,7 +3776,7 @@
       <c r="D37" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E37" s="34" t="s">
+      <c r="E37" s="33" t="s">
         <v>98</v>
       </c>
       <c r="F37" s="9" t="s">
@@ -3790,8 +3831,10 @@
         <f t="shared" si="6"/>
         <v>65.44</v>
       </c>
-      <c r="W37" s="16"/>
-      <c r="X37" s="17">
+      <c r="W37" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X37" s="16">
         <v>46262</v>
       </c>
     </row>
@@ -3808,7 +3851,7 @@
       <c r="D38" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E38" s="34" t="s">
+      <c r="E38" s="33" t="s">
         <v>98</v>
       </c>
       <c r="F38" s="9" t="s">
@@ -3854,87 +3897,89 @@
       <c r="T38" s="5">
         <v>0</v>
       </c>
-      <c r="U38" s="18">
+      <c r="U38" s="17">
         <v>0</v>
       </c>
       <c r="V38" s="14">
         <f t="shared" si="6"/>
         <v>244.18</v>
       </c>
-      <c r="W38" s="16"/>
-      <c r="X38" s="17">
+      <c r="W38" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="X38" s="16">
         <v>46262</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A39" s="36">
+      <c r="A39" s="35">
         <v>65426</v>
       </c>
-      <c r="B39" s="37" t="s">
+      <c r="B39" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="C39" s="38" t="s">
+      <c r="C39" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="D39" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="37" t="s">
+      <c r="D39" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="F39" s="39" t="s">
+      <c r="F39" s="38" t="s">
         <v>108</v>
       </c>
-      <c r="G39" s="38" t="s">
+      <c r="G39" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="H39" s="37" t="s">
+      <c r="H39" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="I39" s="40">
+      <c r="I39" s="39">
         <v>46235</v>
       </c>
-      <c r="J39" s="41">
+      <c r="J39" s="40">
         <v>45.89</v>
       </c>
-      <c r="K39" s="41">
+      <c r="K39" s="40">
         <v>350245.18859999994</v>
       </c>
-      <c r="L39" s="41">
+      <c r="L39" s="40">
         <v>45.89</v>
       </c>
-      <c r="M39" s="41">
+      <c r="M39" s="40">
         <v>350245.18859999994</v>
       </c>
-      <c r="N39" s="41">
+      <c r="N39" s="40">
         <v>35.32</v>
       </c>
-      <c r="O39" s="41">
+      <c r="O39" s="40">
         <v>350245.18859999994</v>
       </c>
-      <c r="P39" s="41">
+      <c r="P39" s="40">
         <v>35.32</v>
       </c>
-      <c r="Q39" s="41">
+      <c r="Q39" s="40">
         <v>350245.18859999994</v>
       </c>
-      <c r="R39" s="41">
-        <v>0</v>
-      </c>
-      <c r="S39" s="41">
-        <v>0</v>
-      </c>
-      <c r="T39" s="41">
-        <v>0</v>
-      </c>
-      <c r="U39" s="41">
-        <v>0</v>
-      </c>
-      <c r="V39" s="42">
+      <c r="R39" s="40">
+        <v>0</v>
+      </c>
+      <c r="S39" s="40">
+        <v>0</v>
+      </c>
+      <c r="T39" s="40">
+        <v>0</v>
+      </c>
+      <c r="U39" s="40">
+        <v>0</v>
+      </c>
+      <c r="V39" s="41">
         <f>SUM(J39,L39,N39,P39,R39,T39)</f>
         <v>162.41999999999999</v>
       </c>
-      <c r="W39" s="41" t="s">
+      <c r="W39" s="40" t="s">
         <v>9</v>
       </c>
       <c r="X39" s="3">
@@ -3945,74 +3990,74 @@
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A40" s="36">
+      <c r="A40" s="35">
         <v>65427</v>
       </c>
-      <c r="B40" s="37" t="s">
+      <c r="B40" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="C40" s="38" t="s">
+      <c r="C40" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="D40" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="37" t="s">
+      <c r="D40" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="F40" s="39" t="s">
+      <c r="F40" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="G40" s="38" t="s">
+      <c r="G40" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="H40" s="37" t="s">
+      <c r="H40" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="I40" s="40">
+      <c r="I40" s="39">
         <v>46235</v>
       </c>
-      <c r="J40" s="41">
+      <c r="J40" s="40">
         <v>55.38</v>
       </c>
-      <c r="K40" s="41">
+      <c r="K40" s="40">
         <v>422667.83069999993</v>
       </c>
-      <c r="L40" s="41">
+      <c r="L40" s="40">
         <v>55.38</v>
       </c>
-      <c r="M40" s="41">
+      <c r="M40" s="40">
         <v>422667.83069999993</v>
       </c>
-      <c r="N40" s="41">
+      <c r="N40" s="40">
         <v>42.62</v>
       </c>
-      <c r="O40" s="41">
+      <c r="O40" s="40">
         <v>422667.83069999993</v>
       </c>
-      <c r="P40" s="41">
+      <c r="P40" s="40">
         <v>42.62</v>
       </c>
-      <c r="Q40" s="41">
+      <c r="Q40" s="40">
         <v>422667.83069999993</v>
       </c>
-      <c r="R40" s="41">
-        <v>0</v>
-      </c>
-      <c r="S40" s="41">
-        <v>0</v>
-      </c>
-      <c r="T40" s="41">
-        <v>0</v>
-      </c>
-      <c r="U40" s="41">
-        <v>0</v>
-      </c>
-      <c r="V40" s="42">
+      <c r="R40" s="40">
+        <v>0</v>
+      </c>
+      <c r="S40" s="40">
+        <v>0</v>
+      </c>
+      <c r="T40" s="40">
+        <v>0</v>
+      </c>
+      <c r="U40" s="40">
+        <v>0</v>
+      </c>
+      <c r="V40" s="41">
         <f t="shared" ref="V40:V42" si="7">SUM(J40,L40,N40,P40,R40,T40)</f>
         <v>196</v>
       </c>
-      <c r="W40" s="41" t="s">
+      <c r="W40" s="40" t="s">
         <v>9</v>
       </c>
       <c r="X40" s="3">
@@ -4020,74 +4065,74 @@
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A41" s="36">
+      <c r="A41" s="35">
         <v>65428</v>
       </c>
-      <c r="B41" s="37" t="s">
+      <c r="B41" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="C41" s="38" t="s">
+      <c r="C41" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="D41" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="37" t="s">
+      <c r="D41" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="F41" s="39" t="s">
+      <c r="F41" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="G41" s="38" t="s">
+      <c r="G41" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="H41" s="37" t="s">
+      <c r="H41" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="I41" s="40">
+      <c r="I41" s="39">
         <v>46235</v>
       </c>
-      <c r="J41" s="41">
+      <c r="J41" s="40">
         <v>18.79</v>
       </c>
-      <c r="K41" s="41">
+      <c r="K41" s="40">
         <v>57712.712499999972</v>
       </c>
-      <c r="L41" s="41">
+      <c r="L41" s="40">
         <v>18.79</v>
       </c>
-      <c r="M41" s="41">
+      <c r="M41" s="40">
         <v>57712.712499999972</v>
       </c>
-      <c r="N41" s="41">
+      <c r="N41" s="40">
         <v>9.75</v>
       </c>
-      <c r="O41" s="41">
+      <c r="O41" s="40">
         <v>57712.712499999972</v>
       </c>
-      <c r="P41" s="41">
+      <c r="P41" s="40">
         <v>9.75</v>
       </c>
-      <c r="Q41" s="41">
+      <c r="Q41" s="40">
         <v>57712.712499999972</v>
       </c>
-      <c r="R41" s="41">
-        <v>0</v>
-      </c>
-      <c r="S41" s="41">
-        <v>0</v>
-      </c>
-      <c r="T41" s="41">
-        <v>0</v>
-      </c>
-      <c r="U41" s="41">
-        <v>0</v>
-      </c>
-      <c r="V41" s="42">
+      <c r="R41" s="40">
+        <v>0</v>
+      </c>
+      <c r="S41" s="40">
+        <v>0</v>
+      </c>
+      <c r="T41" s="40">
+        <v>0</v>
+      </c>
+      <c r="U41" s="40">
+        <v>0</v>
+      </c>
+      <c r="V41" s="41">
         <f t="shared" si="7"/>
         <v>57.08</v>
       </c>
-      <c r="W41" s="43" t="s">
+      <c r="W41" s="42" t="s">
         <v>9</v>
       </c>
       <c r="X41" s="3">
@@ -4095,74 +4140,74 @@
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A42" s="36">
+      <c r="A42" s="35">
         <v>65429</v>
       </c>
-      <c r="B42" s="37" t="s">
+      <c r="B42" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="C42" s="38" t="s">
+      <c r="C42" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="D42" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" s="37" t="s">
+      <c r="D42" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="F42" s="39" t="s">
+      <c r="F42" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="G42" s="38" t="s">
+      <c r="G42" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="H42" s="37" t="s">
+      <c r="H42" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="I42" s="40">
+      <c r="I42" s="39">
         <v>46235</v>
       </c>
-      <c r="J42" s="41">
+      <c r="J42" s="40">
         <v>6.66</v>
       </c>
-      <c r="K42" s="41">
+      <c r="K42" s="40">
         <v>50813.96469999999</v>
       </c>
-      <c r="L42" s="41">
+      <c r="L42" s="40">
         <v>6.66</v>
       </c>
-      <c r="M42" s="41">
+      <c r="M42" s="40">
         <v>50813.96469999999</v>
       </c>
-      <c r="N42" s="41">
+      <c r="N42" s="40">
         <v>5.12</v>
       </c>
-      <c r="O42" s="41">
+      <c r="O42" s="40">
         <v>50813.96469999999</v>
       </c>
-      <c r="P42" s="41">
+      <c r="P42" s="40">
         <v>5.12</v>
       </c>
-      <c r="Q42" s="41">
+      <c r="Q42" s="40">
         <v>50813.96469999999</v>
       </c>
-      <c r="R42" s="41">
-        <v>0</v>
-      </c>
-      <c r="S42" s="41">
-        <v>0</v>
-      </c>
-      <c r="T42" s="41">
-        <v>0</v>
-      </c>
-      <c r="U42" s="41">
-        <v>0</v>
-      </c>
-      <c r="V42" s="42">
+      <c r="R42" s="40">
+        <v>0</v>
+      </c>
+      <c r="S42" s="40">
+        <v>0</v>
+      </c>
+      <c r="T42" s="40">
+        <v>0</v>
+      </c>
+      <c r="U42" s="40">
+        <v>0</v>
+      </c>
+      <c r="V42" s="41">
         <f t="shared" si="7"/>
         <v>23.560000000000002</v>
       </c>
-      <c r="W42" s="43" t="s">
+      <c r="W42" s="42" t="s">
         <v>9</v>
       </c>
       <c r="X42" s="3">
@@ -4170,74 +4215,74 @@
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A43" s="36">
+      <c r="A43" s="35">
         <v>65431</v>
       </c>
-      <c r="B43" s="37" t="s">
+      <c r="B43" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="C43" s="36" t="s">
+      <c r="C43" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="D43" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="E43" s="37" t="s">
+      <c r="D43" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="F43" s="44" t="s">
+      <c r="F43" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="G43" s="36" t="s">
+      <c r="G43" s="35" t="s">
         <v>117</v>
       </c>
-      <c r="H43" s="37" t="s">
+      <c r="H43" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="I43" s="45">
+      <c r="I43" s="44">
         <v>46235</v>
       </c>
-      <c r="J43" s="46">
+      <c r="J43" s="45">
         <v>56.95</v>
       </c>
-      <c r="K43" s="46">
+      <c r="K43" s="45">
         <v>174920.42099999997</v>
       </c>
-      <c r="L43" s="46">
+      <c r="L43" s="45">
         <v>56.95</v>
       </c>
-      <c r="M43" s="46">
+      <c r="M43" s="45">
         <v>174920.42099999997</v>
       </c>
-      <c r="N43" s="46">
+      <c r="N43" s="45">
         <v>29.56</v>
       </c>
-      <c r="O43" s="46">
+      <c r="O43" s="45">
         <v>174920.42099999997</v>
       </c>
-      <c r="P43" s="46">
+      <c r="P43" s="45">
         <v>29.56</v>
       </c>
-      <c r="Q43" s="46">
+      <c r="Q43" s="45">
         <v>174920.42099999997</v>
       </c>
-      <c r="R43" s="46">
-        <v>0</v>
-      </c>
-      <c r="S43" s="46">
-        <v>0</v>
-      </c>
-      <c r="T43" s="46">
-        <v>0</v>
-      </c>
-      <c r="U43" s="46">
-        <v>0</v>
-      </c>
-      <c r="V43" s="47">
+      <c r="R43" s="45">
+        <v>0</v>
+      </c>
+      <c r="S43" s="45">
+        <v>0</v>
+      </c>
+      <c r="T43" s="45">
+        <v>0</v>
+      </c>
+      <c r="U43" s="45">
+        <v>0</v>
+      </c>
+      <c r="V43" s="46">
         <f>SUM(T43,R43,P43,N43,L43,J43)</f>
         <v>173.01999999999998</v>
       </c>
-      <c r="W43" s="46" t="s">
+      <c r="W43" s="45" t="s">
         <v>9</v>
       </c>
       <c r="X43" s="3">
@@ -4245,74 +4290,74 @@
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A44" s="36">
+      <c r="A44" s="35">
         <v>65432</v>
       </c>
-      <c r="B44" s="37" t="s">
+      <c r="B44" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="C44" s="36" t="s">
+      <c r="C44" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="D44" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="37" t="s">
+      <c r="D44" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="F44" s="44" t="s">
+      <c r="F44" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="G44" s="36" t="s">
+      <c r="G44" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="H44" s="37" t="s">
+      <c r="H44" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="I44" s="45">
+      <c r="I44" s="44">
         <v>46235</v>
       </c>
-      <c r="J44" s="46">
+      <c r="J44" s="45">
         <v>45.56</v>
       </c>
-      <c r="K44" s="46">
+      <c r="K44" s="45">
         <v>236948.35645000002</v>
       </c>
-      <c r="L44" s="46">
+      <c r="L44" s="45">
         <v>45.56</v>
       </c>
-      <c r="M44" s="46">
+      <c r="M44" s="45">
         <v>236948.35645000002</v>
       </c>
-      <c r="N44" s="46">
+      <c r="N44" s="45">
         <v>30.17</v>
       </c>
-      <c r="O44" s="46">
+      <c r="O44" s="45">
         <v>236948.35645000002</v>
       </c>
-      <c r="P44" s="46">
+      <c r="P44" s="45">
         <v>30.17</v>
       </c>
-      <c r="Q44" s="46">
+      <c r="Q44" s="45">
         <v>236948.35645000002</v>
       </c>
-      <c r="R44" s="46">
-        <v>0</v>
-      </c>
-      <c r="S44" s="46">
-        <v>0</v>
-      </c>
-      <c r="T44" s="46">
-        <v>0</v>
-      </c>
-      <c r="U44" s="46">
-        <v>0</v>
-      </c>
-      <c r="V44" s="47">
+      <c r="R44" s="45">
+        <v>0</v>
+      </c>
+      <c r="S44" s="45">
+        <v>0</v>
+      </c>
+      <c r="T44" s="45">
+        <v>0</v>
+      </c>
+      <c r="U44" s="45">
+        <v>0</v>
+      </c>
+      <c r="V44" s="46">
         <f t="shared" ref="V44" si="8">SUM(T44,R44,P44,N44,L44,J44)</f>
         <v>151.46</v>
       </c>
-      <c r="W44" s="46" t="s">
+      <c r="W44" s="45" t="s">
         <v>9</v>
       </c>
       <c r="X44" s="3">
